--- a/data/llm_cfs_report_questions.xlsx
+++ b/data/llm_cfs_report_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JackWu/git_project/crc-streamlit-app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BEACC3-DC28-274E-B816-22241A64F79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A37E5B-58CE-664D-AF95-8A6E980065BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28480" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,128 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="174">
-  <si>
-    <t>P250690002241</t>
-  </si>
-  <si>
-    <t>病歷號:OOOOOOO
- 姓  名:OOO            大腸鏡檢查過程記錄暨報告
- 生  日:西元 OOOOOOOO
-                                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20201012            性別: M               流水序號:  報告流水號
-          Start time: 11  時 06 分 12 秒
-     Reach cecum at : 11  時 11 分 13 秒
-          End  time:  11  時 32 分 36 秒
- Clinical Diagnosis :
-   positive iFOBT
- Indication :
-   國民健康署糞便潛血檢查陽性
- Colon preparation agent :
-   PEG-ELS類
- Cleansing time :
-   Morning single dose
- Cleansing Level :
-   Fair
- Instrument :
-   CF            
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   None
- Accessibility :
-   fair
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   Up to cecum, some fecal material was noted inside colon.
-   Out-punching lesions was noted over cecum and A-colon.
-   One 2.2cm LST-G was noted over cecum.
-   One 0.2cm 0-IIa polyp was noted over A-colon s/p biopsy removal(A)
-   One 0.3cm 0-IIa polyp was noted over hepatic flexure s/p biopsy removal(B)
-   One 0.5cm 0-Is polyp was noted over D-colon s/p polypectomy(C) followed by 
-   hemoclipping x I
-   One 0.7cm 0-Is polyp was noted over S-colon s/p polypectomy(D) followed by 
-   hemoclipping x I
-   Mixed hemorrhoid was noted.
- Endoscopic diagnosis :
-   Tubular adenoma,IIa,Ascending colon,0.2cm,S/p biopsy,(A)
-   Tubular adenoma,IIa,Hepatic flexure,0.3cm,S/p biopsy,(B)
-   Tubular adenoma,Is,Descending colon,0.5cm,S/p hot snare polypectomy,S/p 
-   hemoclipping,(c)
-   Tubular adenoma,Is,Sigmoid colon,0.7cm,S/p hot snare polypectomy,S/p 
-   hemoclipping,(D)
-   Colonic diverticulosis,Cecum,Ascending colon
-   Tubular adenoma,LST-G(Laterally spreading tumor,granular type),Cecum,Not 
-   managed : Difficult in management
-   Mixed hemorrhoids
- Complication :
-   NIL
- Suggestion :
-   post-EMR care and pursue the pathology result
-   Diffuse about management of cecal LST-G, ESD or surgical intervention?
-   助理:   
- 檢查者:                          /                       /OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, colon, ascending, labeled as A, colonoscopic biopsy, tubular adenoma
-Intestine, large, colon, hepatic flexure, labeled as B, colonoscopic biopsy, chronic inflammation
-Intestine, large, colon, descending, labeled as C, colonoscopic polypectomy, tubular adenoma
-Intestine, large, colon, sigmoid, labeled as D, colonoscopic polypectomy, tubular adenoma
-Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
-MACROSCOPIC:
-1. Lesion site: 
-    A: Ascending colon     B: Hepatic flexure     C: Descending colon
-    D: Sigmoid
-2. Specimen type: 
-    A: Biopsy      B: Biopsy      C: Polypectomy      D: Polypectomy
-3. Quantity: 
-    A: One tissue fragment, 0.1 x 0.1 x 0.1 cm in size
-    B: One tissue fragment, 0.05 x 0.05 x 0.05 cm in size
-    C: One tissue fragment, 0.3 x 0.3 x 0.2 cm in size
-    D: One tissue fragment, 0.4 x 0.25 x 0.25 cm in size
-4. Comment: Nil
-All for section and labeled as:                  Jar 0
-    A: Ascending colon     B: Hepatic flexure     C: Descending colon
-    D: Sigmoid
-MICROSCOPIC:
-1. Histological diagnosis:
-Neoplastic polyp
-I. Adenoma: 
-    A: Tubular adenoma      C: Tubular adenoma      D: Tubular adenoma
-2. Histological grade:
-    A: Low grade dysplasia (including mild and moderate dysplasia)
-    C: Low grade dysplasia (including mild and moderate dysplasia)
-    D: Low grade dysplasia (including mild and moderate dysplasia)
-3. Margins status (including stalk):
-    A: Not applicable.      C: Margin cannot be assessed.
-    D: Margin uninvolved by tumor. 
-4. Comment: 
-    The section B shows chronic inflammation.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Ascending colon, S/p biopsy, 0.2cm.
-B: Tubular adenoma, Hepatic flexure, S/p biopsy, 0.3cm.
-C: Tubular adenoma, Descending colon, S/p hot snare polypectomy, S/p hemoclipping, 0.5cm.
-D: Tubular adenoma, Sigmoid colon, S/p hot snare polypectomy, S/p hemoclipping, 0.7cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 4 (less than 10mm: 4, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="174">
   <si>
     <t>3-5 Years</t>
   </si>
@@ -445,99 +324,6 @@
 Here are the integrated labels:
 A: Tubular adenoma, Ascending colon, S/p cold snare polypectomy and hemoclipping, 0.6cm.
 B: Tubular adenoma, Hepatic flexure, S/p biopsy removal, 0.3cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 2 (less than 10mm: 2, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
-  </si>
-  <si>
-    <t>P250690006381</t>
-  </si>
-  <si>
-    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20240909
-          Start time:    14 時  51 分 48 秒
-     Reach cecum at :    14 時  55 分 29 秒
-          End  time:     15 時  07 分 43 秒
- Clinical Diagnosis :
-   Positive FIT
- Indication :
-   國民健康署糞便潛血檢查陽性
- Colon preparation agent :
-   Bowclean
- Cleansing time :
-   Split dose
- Cleansing Level :
-   Good
- Instrument :
-   CF-HQ290I                    .21
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   Nil
- Accessibility :
-   Easy
- Anti-platelet / Anti-coagulant agents :
-   Nil
- Colonoscopic Findings :
-   The scope reach to cecum, a 0.5cm 0-Is polyp at A-colon s/p CSP(A). A 0.6cm 
-   0-Is polyp at splenic flexure s/p CSP(B). A 4cm LST-G at rectum. Internal 
-   hemorrhoid was noted.
- Endoscopic diagnosis :
-   Tubular adenoma,Is,Ascending colon,0.5cm,S/p cold snare polypectomy,(A)
-   Tubular adenoma,Is,Splenic flexure,0.6cm,S/p cold snare polypectomy,(B)
-   Tubulovillous adenoma,LST-G(Laterally spreading tumor,granular 
-   type),Rectum,4cm,Not managed : Difficulty in management (will resect at 
-   another session of colonoscopy)
-   Internal hemorrhoid
- Complication :
-   NIL
- Suggestion :
-   Refer for ESD evaluation
-   Consider surgery if ESD infeasible
- 技術員:OOO
- 檢查者:OOO          / 住院醫師:          OOO主治醫師:OOO主治醫師(台消內專證OOOO號)</t>
-  </si>
-  <si>
-    <t>Intestine, large, ascending colon, colonoscopic polypectomy, tubular adenoma
-Intestine, large, splenic flexure, colonoscopic polypectomy, tubular adenoma
-MACROSCOPIC:
-A: 1 tissue fragment (s), (up to) 0.8 x 0.5 x 0.3 cm in size
-B: 3 tissue fragment (s), (up to) 0.5 x 0.2 x 0.1 cm in size
-All for section and labeled as:      Jar 0
-A1: A-colon
-B1: Splenic flexure
-MICROSCOPIC:
-* Histological diagnosis:
-A: tubular adenoma
-B: tubular adenoma
-* High grade dysplasia (including severe dysplasia and carcinoma in situ): Absent
-* Surgical margin:
-A: Cannot be assessed
-B: Cannot be assessed
-Ref: 
-新竹 H2206285</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.5cm.
-B: Tubular adenoma, Splenic flexure, S/p cold snare polypectomy, 0.6cm.
 ------------------------------------------------------------
 2. Clinical Findings Summary:
 ------------------------------------------------------------
@@ -676,271 +462,10 @@
 3-5 Years</t>
   </si>
   <si>
-    <t>P250690003632</t>
-  </si>
-  <si>
-    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20230220
-          Start time:       時     分    秒
-     Reach cecum at :       時     分    秒
-          End  time:        時     分    秒
- Clinical Diagnosis :
-   ..
- Indication :
-   ..
- Colon preparation agent :
-   Magnesium citrate類
- Cleansing time :
-   Evening single dose
- Cleansing Level :
-   Fair
- Instrument :
-   CF-H290I                     212
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   None
- Accessibility :
-   Fair
- Anti-platelet / Anti-coagulant agents :
-   不詳
- Colonoscopic Findings :
-   The previous anastomotic site was noted 10cm above anal verge. A lateral 
-   speading lesion(1.8cm) was noted at T-colon, EMR after saline injectipon was 
-   done(A)(clipx4). A 0.5cm polyp at T-colon, poplypectomy x1(B). A 0.5cm polyp 
-   at D-colon, polypectpomy x1(C).
- Endoscopic diagnosis :
-   Tubular adenoma,LST-G(Laterally spreading tumor,granular type),Transverse 
-   colon,1.8cm,S/p hot EMR (Endoscopic muscosal resection),(A)
-   Tubular adenoma,Ip,Transverse colon,0.5cm,S/p cold snare polypectomy,(B)
-   Tubular adenoma,Ip,Descending colon,0.5cm,S/p cold snare polypectomy,(C)
-   S/P partial colectomy
- Complication :
-   NIL
- Suggestion :
-   Nil
-     技術員:OOOO
-     檢查者:OOO                      / OOO主治醫師(台消內專科證字第806號  )</t>
-  </si>
-  <si>
-    <t>PATHOLOGICAL DIAGNOSIS:
-1. Large intestine, labeled "(A) T-colon", colonoscopic mucosal resection: tubulovillous adenoma
-2. Large intestine, labeled "(B) T-colon", colonoscopic polypectomy: tubular adenoma
-3. Large intestine, labeled "(C) D-colon", colonoscopic polypectomy: tubular adenoma
-GROSS:
-Three bottles labeled as following are received:
-1. "(A) T-colon": one piece of tan and elastic tissue fragment measuring 1.6 x 1.4 x 0.4 cm. (block A, totally submitted)
-2. "(B) T-colon": two pieces of tan and elastic tissue fragments measuring 1.0 x 0.1 x0.1 cm. (block B, totally submitted)
-3. "(C) D-colon": one piece of tan and elastic tissue fragment measuring 0.5 x 0.4 x 0.3 cm. (block C, totally submitted)
-The specimens are submitted as above. 
-MICROSCOPIC FINDINGS:
-Section A:
-a. Histological diagnosis: tubulovillous adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section B:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section C:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Transverse colon, S/p hot EMR, 1.8cm.
-B: Tubular adenoma, Transverse colon, S/p cold snare polypectomy, 0.5cm.
-C: Tubular adenoma, Descending colon, S/p cold snare polypectomy, 0.5cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 3 (less than 10mm: 2, 10-19mm: 1, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
     <t>10 Years</t>
   </si>
   <si>
-    <t>P250690009364</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-病歷號:OOOOOOOO             National Taiwan University  Hospital
-姓　名: OOO
-                          大腸鏡檢查過程紀錄暨報告
-生　日: OOOOOOOO                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20170406            性別: M               流水序號:  報告流水號
- Examination time :Start time :  10:29:52         End time :  10:39:11
- Clinical Diagnosis :
-   Polyp history 
- Indication :
-   Polyp history 
- Colon preparation :
-   Niflec
- Condition :
-   Good
- Instrument :
-   CF-H260AI 2902834
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Nil
- Cleansing time :
-   Morning
- Medication history :
-   Nil
- Colonoscopic Findings :
-   Using Olympus, CF-H260AZI colonoscopic examination, it was inserted up to 
-   cecum with visualization of ICV. Good preparation of colonoscopy (3/4). Two 
-   0.2-0.3cm polyps were noted at D-colon, S-colon, s/p Biopsy. Several flat 
-   lesions were noted at RS-colon. Mildly internal hemorrhoids were noted.
- Endoscopic Diagnosis :
-   Colon polyps, two, r/o tubular adenoma, D-colon, S-colon, s/p Biopsy
-   R/o hyperpalstic polyps, RS-colon
-   Interal hemorrhoids, mild
- Complication :
-   Nil
- Suggestion :
-   F/U CFS years later.
- Specimens :
-   1 Bottle
-   助理:   
- 檢查者:                          /                        / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, colon, descending and sigmoid, colonoscopic biopsy, (1)tubular adenoma; (2)inflammatory polyp
-Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
-MACROSCOPIC:
-1. Lesion site: 
-    Descending colon
-    Sigmoid
-2. Specimen type: 
-    Biopsy
-3. Quantity: 
-    Two tissue fragments, up to 0.3 x 0.2 x 0.2 cm in size
-4. Comment: Nil
-All for section.                           Jar 0
-MICROSCOPIC:
-1. Histological diagnosis:
-Neoplastic polyp
-I. Adenoma: 
-    Tubular adenoma 
-2. Histological grade:
-    Low grade dysplasia (including mild and moderate dysplasia)
-3. Margins status (including stalk):
-    Not applicable.
-4. Comment:
-    It shows a tubular adenoma and an inflammatory polyp, respectively.
-Ref:
-Y1609754
-[01]. Intestine, large, colon, ascending, labeled as A, colonoscopic biopsy, tubular adenoma
-[02]. Intestine, large, colon, transverse, labeled as B, colonoscopic biopsy, tubular adenoma
-[03]. Intestine, large, colon, sigmoid, labeled as C, colonoscopic mucosal resection, cauterized effect
-Y1509397 Intestine, large, colon, transverse, colonoscopic polypectomy, tubular adenoma</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Ascending colon, S/p biopsy, 0.2-0.3cm.
-B: Tubular adenoma, Transverse colon, S/p biopsy, 0.2-0.3cm.
-C: Cauterized effect, Sigmoid colon, S/p EMR, (no size mentioned).
-D: Hyperplastic polyps, Rectosigmoid colon, S/p biopsy, (no size mentioned).
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 2 (less than 10mm: 2, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
-  </si>
-  <si>
     <t>P250690006246</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-病歷號:OOOOOOOO             National Taiwan University  Hospital
-姓　名: OOO
-                          大腸鏡檢查過程紀錄暨報告
-生　日: OOOOOOOO                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20190530            性別: M               流水序號:  報告流水號
- Examination time :Start time :  10:25:43         End time :  10:55:03
- Clinical Diagnosis :
-   Diarrhea
- Indication :
-   Diarrhea
- Colon preparation :
-   Niflec
- Condition :
-   Good
- Instrument :
-   CF-H290I  2611572
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Nil
- Cleansing time :
-   Morning
- Medication history :
-   Nil
- Colonoscopic Findings :
-   Using Olympus, CF-H290I colonoscopic examination, it was inserted up to cecum 
-   with visualization of ICV. Good preparation of colonoscopy (3/4). Redundant 
-   colon was noted during procedure. A 0.4cm Isp polyp at A-colon, s/p Biopsy
-   (A). A 0.4cm Isp polyp at A-colon, s/p Biopsy(B). A &gt;2cm granular flat polyp 
-   was noted beside hepatic flexture. A 0.6cm Isp polyp was noted at S-
-   colon, s/p polypectomy with hemoclipping(x1)(C). Hyperemic spots were 
-   scattered at distal D-colon to S-colon. Flat lesions were noted at rectum. 
-   Mildly mixed hemorrhoids were noted. 
- Endoscopic Diagnosis :
-   Colon polyp, favor tubluar adenoma, A-colon, s/p Biopsy(A)
-   Colon polyp, favor tubluar adenoma, A-colon, s/p Biopsy(B)
-   Colon polyp, favor tubluar adenoma, S-colon, s/p polypectomy with 
-   hemoclipping(C)
-   Colon polyp, favor LST, beside hepatic flexture (difficult access)
-   Mixed hemorrhoids, mild
- Complication :
-   Nil
- Suggestion :
-   F/U CFS later.
-   Difficult access to polyp beside hepatic flexture. (Easy abd. pain during 
-   CFS).
- Specimens :
-   3 Bottles
-   助理:   
- 檢查者:                          /                        / OOO主治醫師</t>
   </si>
   <si>
     <t>Intestine, large, colon, ascending, labeled as A, colonoscopic biopsy, tubular adenoma
@@ -966,25 +491,6 @@
    A, B and C: Low grade dysplasia (including mild and moderate dysplasia)
 3. Margins status (including stalk):
    A and B: Not applicable; C: Margin(s) uninvolved</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Ascending colon, S/p Biopsy, 0.4cm.
-B: Tubular adenoma, Ascending colon, S/p Biopsy, 0.4cm.
-C: Tubular adenoma, Sigmoid colon, S/p polypectomy with hemoclipping, 0.6cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 3 (less than 10mm: 3, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
   </si>
   <si>
     <t>P250690002006</t>
@@ -1187,52 +693,6 @@
 3-5 Years</t>
   </si>
   <si>
-    <t>P250690002519</t>
-  </si>
-  <si>
-    <t>內視鏡檢查報告
-[症狀]
-Elevated CEA
-[Endoscopic Findings]
-Scope reached cecum. A 0.8 cm IIa lesion (LST-NG) was noted at A-colon. EMR was done smoothly withouyt any residual lesion. Multiple diveryticulum were noted at A- and S-colon. Colon preparation was very poor.
-[Diagnosis]
-Colon polyp, IIa(LST-NG) tubular adenoma, Ascending colon s/p EMR
-Diverticulosis, Sigmoid colon, Ascending colon
-Poor colon preparation
-Examiner : G135  OOO 醫師 , Checker1 : G135  OOO 醫師 , Checker2 : G135  OOO 醫師</t>
-  </si>
-  <si>
-    <t>The specimen is submitted in two separated bottles labeled as A: stomach and 
-B: colon, respectively, fixed in formalin.  
-       The specimen labeled as A consists of 2 tissue fragments measuring up to 0.2 x 
-0.2 x 0.2 cm. in size.  Grossly, they are yellowish white and soft.        
-       The specimen labeled as B consists of one tissue fragment measuring 1.0 x 0.6 x 0.2
-cm. in size.  Grossly, it is brown and soft.        
-        All for section and labeled as:                                          Jar 0 
-        A: stomach        B: colon
-        Microscopically, section A shows chronic gastritis with no intestinal metaplasia.
-No Helicobacter bacillus is found in the foveolar pits.  Section B reveals a tubular adenoma.
-Ref: S9821217,S9914196,S0213212,S0318212</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Ascending colon, S/p EMR, 0.8cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 1 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
-  </si>
-  <si>
     <t>P250690010542</t>
   </si>
   <si>
@@ -1350,83 +810,6 @@
 ------------------------------------------------------------
 3. 2020 USMSTF recommendation interval
 3-5 Years</t>
-  </si>
-  <si>
-    <t>P250690000036</t>
-  </si>
-  <si>
-    <t>Clinical Diagnosis                                      
-  Positive iFOBT
- Indication                                              
-  國民健康署糞便潛血檢查陽性
- Colon preparation agent                                 
-  Bowclean
- Cleansing time:                                         
-  Split dose                                             
- Cleansing Level:                                        
-  Good                                                   
- Instrument:                                             
-  CF-HQ290I                  .5                
- Insertion level:                                        
-  Cecum                                                  
- Pre-mediction:                                          
-  Hyoscine butylbromide                                  
- Sedation                                                
-  Midazolam(Dormicum)
-  Propofol
-  Fentanyl(含Alfentanyl)
- Accessibility:                                          
-  Easy                                                   
- Anti-platelet/Anti-coagulant agents                     
-  Nil
- Colonoscopic Findings                                   
-  A 0.9cm 0-IIa polyp at cecum s/p polypectomy followed by hemoclipping*1(A). 
-  The 4cm circumferential flat lesion was noted at A-colon. A 0.6cm 0-Is polyp 
-  at D-colon s/p cold-snaring polypectomy(B). Internal hemorrhoid was noted.
- Diagnosis                                                                       檢體總數:                     2           
-  Tubular adenoma,O-lla,Cecum,0.9cm,S/p hemoclipping,(A),S/p hot snare 
-  polypectomy
-  Tubulovillous adenoma, LST-NG, Ascending colon, 4.0cm,Nil(未處置),Difficulty 
-  in management (refer to other hospital)
-  Tubular adenoma,O-ls,Descending colon,0.6cm,(B),S/p cold snare polypectomy
-  Internal hemorrhoid
- Complication                                            
-  Nil
- Suggestion                                              
-  Post polypectomy care and pursue pathology report
-  Refer to medical center for ESD evaluation</t>
-  </si>
-  <si>
-    <t>DIAGNOSIS
-Large intestine, cecum (A), polypectomy
-   ----Tubular adenoma
-Large intestine, D-colon (B), polypectomy
-   ----Tubular adenoma
-GROSS DESCRIPTION
-   The specimen submitted consists of 2 bottles.
-   Bottle A contains a tissue fragment measuring 0.8 x 0.5 x 0.2 cm.
-   Bottle B contains a tissue fragment measuring 0.4 x 0.2 x 0.2 cm.
-   All submitted.
-MICROSCOPIC DESCRIPTION
-   Sections of specimens A and B both show polypoid colonic mucosa with adenomatous glands.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Cecum, S/p hemoclipping and hot snare polypectomy, 0.9cm.
-B: Tubular adenoma, Descending colon, S/p cold snare polypectomy, 0.6cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 2 (less than 10mm: 2, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
   </si>
   <si>
     <t>P250690010461</t>
@@ -1597,111 +980,6 @@
 ------------------------------------------------------------
 3. 2020 USMSTF recommendation interval
 3 Years</t>
-  </si>
-  <si>
-    <t>P250690002816</t>
-  </si>
-  <si>
-    <t>病歷號: OOOOOOO
- 姓  名:OOO             大腸鏡檢查過程紀錄暨報告
- 生  日:西元 OOOOOOO
-                                                                             第 1  頁
-   檢查單號:  OOOOOOOO         年齡: 75              保險身分:   
-   檢查日期:  20240318            性別: F               流水序號:  報告流水號
-          Start time:    11 時  52 分 55 秒
-     Reach cecum at :    12 時  02 分 07 秒
-          End  time:     12 時  35 分 43 秒
- Clinical Diagnosis :
-   Pelvic tumor
- Indication :
-   Pelvic tumor
- Colon preparation agent :
-   Magnesium citrate類
- Cleansing time :
-   Split dose
- Cleansing Level :
-   Good
- Instrument :
-   CF224Z                        
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   Midazolam (Dormicum)
-   Propofol
-   Fentanyl (含Alfentanyl)
- Accessibility :
-   Fair
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   The scope was inserted to the cecum. One 0.7 cm Is NICE type 2 lesion was 
-   noted at the A-colon S/p CSP (lost). One 0.4 cm Is NICE type 2 lesion was 
-   noted at the A-colon S/p CSP (A). One 0.3 cm Is NICE type 2 lesion was noted 
-   at the hepatic flexure S/p CSP (B). One 2.5 cm LST-NG NICE type 1 lesion was 
-   noted at the S-colon, not managed. External hemorrhoids were noted.
- Endoscopic diagnosis :
-   Tubular adenoma,Is,Ascending colon,0.4cm,S/p cold snare polypectomy,(A)
-   Tubular adenoma,Is,Hepatic flexure,0.3cm,S/p cold snare polypectomy,(B)
-   Tubular adenoma,Is,Ascending colon,0.7cm,S/p cold snare polypectomy,(lost)
-   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
-   type),Sigmoid colon,Not managed : Difficulty in management (will resect at 
-   another session of colonoscopy)
-   External hemorrhoids
- Complication :
-   NIL
- Suggestion :
-   The 2.5 cm laterally spreading tumor at sigmoid colon will be evaluated and 
-   managed at another session of colonoscopy (by endoscopic mucosal resection or 
-   endoscopic submucosal dissection).
-     技術員: OOO
-     檢查者:                         / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>PATHOLOGICAL DIAGNOSIS:
-Intestine, large, ascending, labeled A, colonoscopic polypectomy --- tubular adenoma
-Intestine, large, hepatic flexure, labeled B, colonoscopic polypectomy --- tubular adenoma
-GROSS FINDINGS:
-The specimen A submitted consists of 3 tissue fragments measuring up to 0.5 x 0.2 x 0.1 cm in size, fixed in formalin.
-Grossly, they are tan and elastic. 
-All for section and labeled as A.
-The specimen B submitted consists of 2 tissue fragments measuring 0.6 x 0.2 x 0.1 cm and 0.1 x 0.1 x 0.1 cm in size, fixed in formalin.
-Grossly, they are tan and elastic. 
-All for section and labeled as B.
-MICROSCOPIC FINDINGS:
-Specimen A:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high-grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Specimen B:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high-grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.4cm.
-B: Tubular adenoma, Hepatic flexure, S/p cold snare polypectomy, 0.3cm.
-A (lost): Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.7cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 3 (less than 10mm: 3, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
   </si>
   <si>
     <t>P250690012127</t>
@@ -1905,305 +1183,6 @@
     <t>1 Year</t>
   </si>
   <si>
-    <t>P250690005722</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
- 病歷號:  OOOOOO                    National Taiwan University  Hospital
-                                 大腸鏡檢查過程紀錄暨報告
- 姓　名:  OOO
-                                           (內視鏡中心)
- 生　日:  ____/___/___                                                                              第 1    頁
-     檢查單號:    T0145974833              年齡:   50                 保險身分:     
-     檢查日期:    20140610                 性別:   M                  流水序號:    C037611
- Examintion time :      Start time :      11:26:22            End time :      11:57:36
- Clinical Diagnosis :
-    colon cancer s/p LAR
- Indication :
-    Post surgery surveillance
- Colon preparation :
-    Niflec
- Condition :
-    Good
- Instrument :
-    CF-Q260AL    .20
- Insertion level :
-    Cecum
- Pre-medication :
-    Buscopan
- Anesthesia :
-    Nil
- Cleansing time :
-    Evening
- Medication history :
-    Nil
- Colonoscopic Findings :
-    Up to cecum, some fecal material was noted in the colon.
-    s/p LAR. The anastomosis site was around 10cm AAV. No ulcer nor mass lesion 
-    was noted around the anastomosis site.
-    One 1.0cm LST-NG was noted over A-colon. EMR was performed after saline 
-    injection follwed by hemoclipping x III for hemostasis.
-    Mixed hemorrhoid was noted.
- Endoscopic Diagnosis :
-    s/p LAR
-    Colon LST-NG, A-colon, probably tubular adenoma, s/p EMR, s/p hemoclipping.
-    Mixed hemorrhoid.
- Complication :
-    Negative
- Suggestion :
-    Post EMR care and pursue pathology report
- Specimens :
-    1 bottle
-  Assistant :  OOO              Examiner :   OOO      醫師 / OOO      醫師 / OOO      醫師
-                                   報告日期 :   2014/06/10    12:32:40</t>
-  </si>
-  <si>
-    <t>Intestine, large, colon, ascending, status post resection , colonoscopic mucosal resection,hyperplastic polyp
-MACROSCOPIC :
-*Quantity: One tissue fragment, 0.7 x 0.4 x 0.2 cm in size
-All for section                                           Jar 0
-MICROSCOPIC :
-* Histological diagnosis: Hyperplastic polyp
-* High grade dysplasia (including severe dysplasia and carcinoma in situ): 
-   Absent 
-* Invasive carcinoma: Absent  
-* Surgical margin: 
-    Uninvolved 
-* Comment(s):nil
-Ref:
-總院 S1401619
-[01]. Intestine,large,colon,sigmoid,laparoscopic anterior resection, adenocarcinoma,moderately differentiated
-[02]. Lymph node,regional,lymphadenectomy, carcinoma,metastatic,(4/18)
-總院 S1350431
-[01]. Intestine,large,colon,sigmoid,endoscopic biopsy, adenocarcinoma
-總院 S1400460
-[01]. Intestine,large,colon,sigmoid,laparoscopic anterior resection, adenocarcinoma,moderately differentiated
-[02]. Lymph node,regional,lymphadenectomy, carcinoma,metastatic,(4/18)
-總院 M1404003
-[01]. Intestine,large,colon,sigmoid,K-ras/B-Raf Gene Mutation Analysis, see description</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Hyperplastic polyp, Ascending colon, S/p EMR and hemoclipping, 1.0cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
-  </si>
-  <si>
-    <t>P250690001419</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-病歷號:OOOOOOOO             National Taiwan University  Hospital
-姓　名: OOO
-                          大腸鏡檢查過程紀錄暨報告
-生　日: OOOOOOOO                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20250522            性別: M               流水序號:  報告流水號
- Examination time :Start time :  15:50:49         End time :  16:07:12
- Clinical Diagnosis :
-   Colon polyp
- Indication :
-   Post polypectomy surveillance
- Colon preparation :
-   Niflec
- Condition :
-   Good
- Instrument :
-   CF-H2901   
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Intravenous general anesthesia
- Cleansing time :
-   Evening
- Medication history :
-   Nil
- Colonoscopic Findings :
-   Up to cecum, one 0.6cm 0-IIa polyp was noted at ascending colon and cold-
-   snare polypectomy was done as "A". One 3.5cm LST-NG was noted at hepatic 
-   flexure. One 0.5cm 0-IIa polyp was noted at transverse colon and cold-snare 
-   polypectomy was done as "B". One 0.8cm 0-Is polyp was noted at descending 
-   colon and cold-snare polypectomy with hemoclip x 1 was done as "C". One 0.5cm 
-   0-IIa polyp was noted at sigmoid colon and cold-snare polypectomy was done as 
-   "D". Internal hemorrhoid was noted.
- Endoscopic Diagnosis :
-   1.Lateral spreading tumor, non-granular type, hepatic flexure.
-   2.Colon polyp, 0-IIa, ascending colon, s/p cold-snare polypectomy(A).
-   3.Colon polyp, 0-IIa, transverse colon, s/p cold-snare polypectomy(B).
-   4.Colon polyp, 0-Is, descending colon, s/p cold-snare polypectomy with 
-   hemoclipping(C).
-   5.Colon polyp, 0-IIa, sigmoid colon, s/p cold-snare polypectomy(D).
-   6.Internal hemorrhoid.
- Complication :
-   Nil
- Suggestion :
-   Consider ESD or surgical resection of LST at hepatic flexure. Pursue 
-   pathology report and regular follow up.
- Specimens :
-   Four bottles.
-   助理:   
- 檢查者:                          /                        / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, ascending colon (A), colonoscopic polypectomy, tubular adenoma.
-Intestine, large, transverse colon (B), colonoscopic polypectomy, hyperplastic polyp.
-Intestine, large, descending colon (C), colonoscopic polypectomy, tubular adenoma.
-Intestine, large, sigmoid colon (D), colonoscopic polypectomy, hyperplastic polyp.
-Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
-MACROSCOPIC:
-1. Lesion site: 
-    A: ascending colon    B: transverse colon
-    C: descending colon   D: sigmoid colon
-2. Specimen type: 
-    A: polypectomy    B: polypectomy    C: polypectomy   D: polypectomy
-3. Quantity: 
-    A: Three tissue fragments, up to 0.8x0.3x0.1 cm in size
-    B: One tissue fragment, 1.5x0.3x0.1 cm in size
-    C: One tissue fragment, 1x0.4x0.4 cm in size
-    D: One tissue fragment, 0.6x0.3x0.1 cm in size
-4. Comment: Nil 
-All for section and labeled as:                  Jar 0
-    A: ascending colon    B: transverse colon
-    C: descending colon   D: sigmoid colon
-MICROSCOPIC:
-1. Histological diagnosis:
-Neoplastic polyp
-I. Adenoma: 
-Tubular adenoma 
-2. Histological grade:
-Low grade dysplasia (including mild and moderate dysplasia)
-3. Margins status (including stalk):
-Margin(s) uninvolved 
-4. Comment:
-Sections B1 and D1 show hyperplastic polyp.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Ascending colon, S/p cold-snare polypectomy with hemoclipping, 0.6cm.
-B: Hyperplastic polyp, Transverse colon, S/p cold-snare polypectomy, 0.5cm.
-C: Tubular adenoma, Descending colon, S/p cold-snare polypectomy with hemoclipping, 0.8cm.
-D: Hyperplastic polyp, Sigmoid colon, S/p cold-snare polypectomy, 0.5cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 2 (less than 10mm: 2, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
-  </si>
-  <si>
-    <t>P250690013222</t>
-  </si>
-  <si>
-    <t>國 立 台 灣 大 學 醫 學 院 附 設 醫 院
- 病歷號:OOOOOOO            National Taiwan University Hospital 
- 姓  名:OOO           大腸鏡檢查過程紀錄暨報告
- 生  日:西元 OOOOOO           (綜診部內視鏡中心)                           第 1  頁
-   檢查單號:  OOOOOO         年齡: 77              保險身分:   
-   檢查日期:  OOOOOO            性別: M               流水序號:  OOOOOO
-          Start time:    15 時  47 分 36 秒
-     Reach cecum at :    15 時  59 分 51 秒
-          End  time:     16 時  24 分 21 秒
- Clinical Diagnosis :
- Indication :
-   術前評估
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colon preparation agent :
-   PEG-ELS類
- Cleansing time :
-   Morning single dose
- Cleansing Level :
-   Good
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Instrument :
-   CF H290I.2
- Sedation :
-   Midazolam (Dormicum)
-   Propofol
-   Fentanyl (含Alfentanyl)
- Accessibility :
-   Difficult
- Colonoscopic Findings :
-   A &gt;10cm circumferential LSTG at cecum and A/c. Bx was done (A). another 0.5cm 
-   polyp at HF s/p CSP (B).
- Endoscopic diagnosis :
-   Tubular adenoma,LST-G(Laterally spreading tumor,granular type),Ascending 
-   colon,15cm,S/p biopsy,(A)
-   Tubular adenoma,Is,Ascending colon,0.5cm,S/p cold snare polypectomy,(B)
-   External hemorrhoids
- Specimens :
-   2    bottle(s)
- Complication :
-   NIL
- Suggestion :
-   助理:  OOO護理師
- 檢查者:                           /                        / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, colon, ascending, colonoscopic biopsy, tubulovillous adenoma
-Intestine, large, colon, ascending, colonoscopic cold snare polypectomy, tubular adenoma
-MACROSCOPIC:
-A: 5 tissue fragments, up to 0.3 x 0.2 x 0.1 cm in size
-B: 1 tissue fragment, 0.4 x 0.3 x 0.2 cm in size
-All for sections and labeled as:    Jar 0
-A1: ascending colon
-B1: ascending colon
-MICROSCOPIC:
-* Histological diagnosis:
-  A: Tubulovillous adenoma
-  B: Tubular adenoma
-* High grade dysplasia (including severe dysplasia and carcinoma in situ): Absent
-* Surgical margin: 
-  Section A1: Cannot be assessed 
-  Section B1: Uninvolved 
-Ref:
-總院 S2128708
-[01]. Meninx, fronto-parietal, right and left, excision, atypical meningioma, WHO grade 2
-[02]. Bone, skull, fronto-parietal, excision, atypical meningioma involvement
-[03]. Soft tissue, scalp, excision, atypical meningioma involvement</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubulovillous adenoma, Ascending colon, S/p colonoscopic biopsy, 15cm.
-B: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.5cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 1)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: Yes
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
     <t>P250690002785</t>
   </si>
   <si>
@@ -2400,201 +1379,6 @@
     <t>5-10 Years</t>
   </si>
   <si>
-    <t>P250690000731</t>
-  </si>
-  <si>
-    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: F         檢查日期: 20241023
-          Start time:    15 時  35 分 37 秒
-     Reach cecum at :    15 時  38 分 06 秒
-          End  time:     16 時  05 分 09 秒
- Clinical Diagnosis :
-   iFOBT positive
- Indication :
-   iFOBT positive
- Colon preparation agent :
-   Phosphosoda類
-   Magnesium citrate類
- Cleansing time :
-   Split dose
- Cleansing Level :
-   Excellent
- Instrument :
-   CF-H290I                     5
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   Midazolam (Dormicum)
-   Propofol
-   Fentanyl (含Alfentanyl)
- Accessibility :
-   Easy
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   The scope was inserted into cecum. There was a 3.0cm adenoomatous fungating 
-   lesion, located at upper rectum, with lowest border at 10cm AAV. Un-lifting 
-   sign was observed after submucosal injection. Early rectal cancer was 
-   suspected. Biopsy was taken, followed with ink injection as tattooing 
-   localization(A).
- Endoscopic diagnosis :
-   Early colorectal cancer,LST-NG(Laterally spreading tumor,non-granular 
-   type),Rectum,3cm,S/p biopsy,S/p tattooing,(A)
- Complication :
-   NIL
- Suggestion :
-   Pursue pathology report
- 技術員:OOO
- 檢查者:OOO       / 住院醫師:          OOO主治醫師:OOO主治醫師(台消外專科證字第OOOO號)</t>
-  </si>
-  <si>
-    <t>Intestine, large, rectum, upper, endoscopic biopsy, at least focal high-grade dysplasia, in background of tubulovillous adenoma (see description)
-[Gross examination]
-1. Specimen size: nine, up to 0.5 x 0.3 x 0.1 cm
-2. Tissue origin: rectum, upper
-3. Gross description: tan and elastic
-  All for sections. Jar 0 
-[Microscopic description]
-a. Histological diagnosis: tubulovillous adenoma
-b. Histological grade: High grade dysplasia 
-c. Margin status (for high grade dysplasia or carcinoma):Not applicable 
-d. Lymphovascular invasion: Not applicable 
-e. Perineural invasion: Not applicable
-f. Comments: 
-   It shows fragments of tubulovillous adenoma with focal high-grade dysplasia. No definite evidence of invasive carcinoma is concluded in original and deeper sections. However, a few atypical cells are noted in the stroma under CK(AE1/AE3) immunostain. Invasive carcinoma cannot be ruled out completely as the specimen is mostly superficial and little lamina propria component is included. 
-Please also correlate with endoscopic findings. 
-Ref: 
-新竹 H2415151
-新竹 H2181379
-新竹 H2105113
-[01]. Breast, right, simple mastectomy, invasive lobular carcinoma
-新竹 H2105111
-[01]. Breast, right (UIQ), partial mastectomy, ductal carcinoma in situ</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubulovillous adenoma, Rectum, S/p endoscopic biopsy, 3.0cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 1)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: Yes
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
-    <t>P250690007694</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-病歷號:OOOOOOOO             National Taiwan University  Hospital
-姓　名: OOO
-                          大腸鏡檢查過程紀錄暨報告
-生　日: OOOOOOOO                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20201028            性別: M               流水序號:  報告流水號
- Examination time :Start time :                   End time :   
- Clinical Diagnosis :
-   Post surgery surveillance
- Indication :
-   Post surgery surveillance
- Colon preparation :
-   Niflec
- Condition :
-   Fair
- Instrument :
-   CF-Q260AL 2722499
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Dromucum+Rapifen+Propofol
- Cleansing time :
-   Morning
- Medication history :
-   Nil
- Colonoscopic Findings :
-   The scope had been inserted up to cecum with visualization of ICV. Much stool 
-   materials was found.
-   A colon lesion with predominant spread within the mucosa while still 
-   relatively flat (Kudo pattern IIIL), up to 1.0cm in size,was noted at 
-   Ascending  colon, at 68 cm above the anal verge.Anther 0.5 cm IIa colon polyp 
-   was found over Ascending  colon, at 68 cm above the anal verge.Biopsy was 
-   performed to remove the lesion(A).
-   Anther 0.5 cm IIa colon polyp was found over Sigoid colon, at 25 cm above the 
-   anal verge. Biopsy was performed to remove the lesion. Internal hemorrhoid 
-   was noted.
- Endoscopic Diagnosis :
-   Probably,Lateral spreading tumors (LST),Ascending colon s/p biopsy removal(A)
-   Tubular adenoma,0.5cm, 0-IIa,Ascending colon,s/p biopsy removal(A)
-   Probably,Tubular adenoma,0.5cm,0-IIa,Sigmoid colon,s/p biopsy removal(B)
-   Probably,Internal hemorrhoid
- Complication :
-   Nil
- Suggestion :
-   Follow up CFS next year
-   Post biopsy care and pursue pathology report
- Specimens :
-   2 Bottles
-   助理:   
- 檢查者:                          /                        / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Ascending colon polyps, labeled as A, biopsy removal: tubular adenomas 
-Sigmoid colon polyp, labeled as B, biopsy removal: tubular adenoma
-Colon Neoplastic polyp checklists
-2013/07/19病理部品管會議通過第一版
-MACROSCOPIC :
-1.	Lesion site : 
-A: Ascending colon
-B: Sigmoid
-2.	Specimen type : 
-A and B: Biopsy
-3.	Quantity: 
-The specimen A submitted consists of 2 tissue fragments measuring 0.2-0.3 cm in formalin. Total tissue is submitted in cassette A.
-The specimen B submitted consists of 1 tissue fragment measuring 0.2 cm fixed in formalin. Total tissue is submitted in cassette B.
-MICROSCOPIC:
-1.	Histological diagnosis:
-Neoplastic polyp
-I.	Adenoma: 
-A and B: Tubular adenoma 
-2.	Histological grade:
-A and B: Low grade dysplasia (including mild and moderate dysplasia)</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Ascending colon, S/p biopsy removal, 0.5cm.
-B: Tubular adenoma, Sigmoid colon, S/p biopsy removal, 0.5cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 2 (less than 10mm: 2, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
-  </si>
-  <si>
     <t>P250690009072</t>
   </si>
   <si>
@@ -2701,226 +1485,6 @@
 10 Years</t>
   </si>
   <si>
-    <t>P250690003436</t>
-  </si>
-  <si>
-    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20230621
-          Start time:    13 時  57 分 08 秒
-     Reach cecum at :    13 時  59 分 22 秒
-          End  time:     14 時  20 分 37 秒
- Clinical Diagnosis :
-   Bloody stool
- Indication :
-   Bloody stool
- Colon preparation agent :
-   Phosphosoda類
- Cleansing time :
-   Split dose
- Cleansing Level :
-   Excellent
- Instrument :
-   CF-H290I                     211
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   Midazolam (Dormicum)
-   Propofol
-   Fentanyl (含Alfentanyl)
- Accessibility :
-   Easy
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   The scope was inserted into cecum. There was a 0.5cm 0-Is adenoma, located at 
-   splenic flexure, cold snare polypectomy was done(A). There were two 0.5cm 0-
-   Is adenoma, located at D-colon, cold snare polypectomies were done(B). There 
-   was a 2.0cm lateral spreading submucosal lesion, with smooth mucosal surface, 
-   located at D-S junction, nature unknown, benign lesion more suspected, s/p 
-   tattooing localization(E) for better follow up. There were three 0.5cm 0-Is 
-   adenoma, located at S-colon, cold snare polypectomies were done(C). There was 
-   a 0.5cm 0-Is adenoma, located at rectum, cold snare polypectomy was done(D). 
-   (Total 7 polyps removed)
- Endoscopic diagnosis :
-   Tubular adenoma,Is,Splenic flexure,0.5cm,S/p cold snare polypectomy,(A)
-   Tubular adenoma,Is,Descending colon,0.5cm,S/p cold snare polypectomy,(B)
-   Tubular adenoma,Is,Sigmoid colon,0.5cm,S/p cold snare polypectomy,(C)
-   Tubular adenoma,Is,Rectum,0.5cm,S/p cold snare polypectomy,(D)
-   Submucosal tumor,LST-NG(Laterally spreading tumor,non-granular 
-   type),Descending colon,2cm,S/p tattooing,(E)
- Complication :
-   NIL
- Suggestion :
-   post polypectomy care
-   regular CFS f/u for SMT at DS junction
- 技術員:OOO
- 檢查者:OOO       / 住院醫師:          OOO主治醫師:OOO主治醫師(台消外專科證字第OOOO號)</t>
-  </si>
-  <si>
-    <t>PATHOLOGICAL DIAGNOSIS:
-1. Large intestine, labeled "(A) splenic flexure", colonoscopic cold snare polypectomy: tubular adenoma
-2. Large intestine, labeled "(B) D-colon", colonoscopic cold snare polypectomy: hyperplastic polyp
-3. Large intestine, labeled "(C) S-colon", colonoscopic cold snare polypectomy: tubular adenoma
-4. Large intestine, labeled "(D) rectum", colonoscopic cold snare polypectomy: tubular adenoma
-GROSS:
-Four bottles labeled as following are received:
-1. "(A) splenic flexure": six pieces of tan and elastic tissue fragments measuring 0.5 x 0.3 x 0.1 cm. (block A, totally submitted)
-2. "(B) D-colon": three pieces of tan and elastic tissue fragments measuring 1.2 x 0.3 x 0.1 cm. (block B, totally submitted)
-3. "(C) S-colon": five pieces of tan and elastic tissue fragments measuring 0.7 x 0.3 x 0.1 cm. (block C, totally submitted)
-4. "(D) rectum": one piece of tan and elastic tissue fragment measuring 0.9 x 0.5 x 0.2 cm. (block D, totally submitted)
-The specimens are submitted as above. 
-MICROSCOPIC FINDINGS:
-Section A:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section B:
-a. Histological diagnosis: hyperplastic polyp
-b. Histological grade: not applicable
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section C:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section D:
-a. Histological diagnosis: tubular adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Splenic flexure, S/p cold snare polypectomy, 0.5cm.
-B: Hyperplastic polyp, Descending colon, S/p cold snare polypectomy, 0.5cm.
-C: Tubular adenoma, Sigmoid colon, S/p cold snare polypectomy, 0.5cm.
-D: Tubular adenoma, Rectum, S/p cold snare polypectomy, 0.5cm.
-E: LST-NG (Laterally spreading tumor, non-granular type), Descending colon, S/p tattooing, 2cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 3 (less than 10mm: 3, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
-  </si>
-  <si>
-    <t>P250690003628</t>
-  </si>
-  <si>
-    <t>Clinical Diagnosis                                      
-  Acute diarrhea
- Indication                                              
-  Bloody stool
- Colon preparation agent                                 
-  PEG-ELS 類
- Cleansing time:                                         
-  Morning single dose                                    
- Cleansing Level:                                        
-  Fair                                                   
- Instrument:                                             
-  CF-HQ290I                  .2                
- Insertion level:                                        
-  Cecum                                                  
- Pre-mediction:                                          
-  Hyoscine butylbromide                                  
- Sedation                                                
-  Nil
- Accessibility:                                          
-  Easy                                                   
- Anti-platelet/Anti-coagulant agents                     
-  Nil
- Colonoscopic Findings                                   
-  Much fecal materials were found over cecum. A 0.7cm 0-IIa polyp at cecum s/p 
-  EMR followed by hemoclipping*2(A). A 1.2cm 0-Ip polyp at S-colon s/p 
-  polypectomy followed by hemoclipping*2. A 0.3cm 0-Is polyp at S-colon s/p 
-  polypectomy. Two polyps collected as sample (B). The 1.2cm erythematous 
-  villous lesion were found at lower rectum near anus s/p biopsy*2(C). Internal 
-  hemorrhoid was noted. 
- Diagnosis                                                                       檢體總數:                     3           
-  Sessile serrated adenoma,O-lla,Cecum,0.7cm,S/p EMR (Endoscopic mucosal 
-  resection),S/p hemoclipping,(A)
-  Tubulovillous adenoma,O-lp,Sigmoid colon,1.2cm,S/p hemoclipping,(B),S/p hot 
-  snare polypectomy
-  Tubular adenoma,O-ls,Sigmoid colon,0.3cm,(B),S/p polypectomy
-  Tubulovillous adenoma,LST-NG(Laterally spreading tumor,non-granular 
-  type),Rectum,S/p biopsy,(C)
-  Internal hemorrhoid
- Complication                                            
-  Nil
- Suggestion                                              
-  1. Post EMR care and pursue pathology report
-  2. The lesion near lower rectum near anus could not managed by endoscope due 
-  to the position.</t>
-  </si>
-  <si>
-    <t>PATHOLOGICAL DIAGNOSIS:
-1. Colon, cecum, EMR: tubular adenoma
-2. Colon, S-colon, colonoscopic polypectomy: tubulovillous adenoma
-3. Colon, rectum, colonoscopic biopsy: adenomatous change. 
-GROSS:
-1. Bottle A: one tissue fragment, 0.8x0.6x0.3 cm in size.
-2. Bottle B: 2 tissue fragments, up to 1x0.7x0.6 cm in size.
-3. Bottle C: 2 tissue fragments, up to 0.4x0.1x0.1 cm in size.
-The entire specimen is submitted in cassettes, labeled A: cecum, B1-2: S-colon, C: rectum.
-MICROSCOPIC FINDINGS:
-1. Bottle A:
-a. Histological diagnosis: Tubular adenoma
-b. Histological grade: Low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): Not applicable
-d. Lymphovascular invasion: Not applicable
-e. Perineural invasion: Not applicable
-f. Comments: nil.
-2. Bottle B:
-a. Histological diagnosis: Tubulovillous adenoma
-b. Histological grade: Low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): Not applicable
-d. Lymphovascular invasion: Not applicable
-e. Perineural invasion: Not applicable
-f. Comments: nil.
-3. Bottle C:
-Sections show fragments of colon mucosa with adenomatous change. No high grade dysplasia or stromal invasion is identified in examined specimen. Clinical correlation and further evaluation are recommended.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubular adenoma, Cecum, S/p EMR and S/p hemoclipping, 0.7cm.
-B: Tubulovillous adenoma, Sigmoid colon, S/p hemoclipping and S/p hot snare polypectomy, 1.2cm.
-B: Tubular adenoma, Sigmoid colon, S/p polypectomy, 0.3cm.
-C: Adenomatous change, Rectum, S/p biopsy, 1.2cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 3 (less than 10mm: 2, 10-19mm: 1, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: Yes
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
     <t>endoscopy_report</t>
   </si>
   <si>
@@ -2940,9 +1504,6 @@
   </si>
   <si>
     <t>7-10y</t>
-  </si>
-  <si>
-    <t>3-5y</t>
   </si>
   <si>
     <t>P250690002234</t>
@@ -3047,159 +1608,7 @@
 7-10 Years</t>
   </si>
   <si>
-    <t>P250690003250</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-病歷號:OOOOOOOO             National Taiwan University  Hospital
-姓　名: OOO美
-                          大腸鏡檢查過程紀錄暨報告
-生　日: OOOOOOOO                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20231130            性別: F               流水序號:  報告流水號
- Examination time :Start time :                   End time :   
- Clinical Diagnosis :
-   Poor appetite.
- Indication :
-   Poor appetite.
- Colon preparation :
-   Niflec
- Condition :
-   Good
- Instrument :
-   CF-H2901  2045596
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Nil.
- Cleansing time :
-   Morning
- Medication history :
-   Nil
- Colonoscopic Findings :
-   The scope had been inserted up to cecum with visualization of ICV. 
-   Hemoclips x 1 was applied to close the wound.
-   A 2.0 cm flat lesion was noted at ascending colon colon colon, at 68 cm above 
-   the anal verge.Then glyceroal 5 mL injected to lift the lesion. The lesion 
-   was resected by snare. Hemoclips x 3 was applied to close the wound.
-   Internal hemorrhoid was noted.
- Endoscopic Diagnosis :
-   Probably,Laterally Spreading Tumor,2.0cm,Ascending colon,S/P EMR (Endoscopic 
-   mucosal resection),S/P Hemoclipping.
-   Probably,Internal hemorrhoid
- Complication :
-   Nil
- Suggestion :
-   Follow up CFS next year
-   Post EMR care and pursue pathology report
-   Beware of bleeding sign,educated avoid heavy work.
- Specimens :
-   1 Bottles
-   助理:   
- 檢查者:                          /                        / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, ascending colon, colonoscopic EMR, sessile serrated lesion.
-MACROSCOPIC:
-1. Lesion site: 
-    ascending colon
-2. Specimen type: 
-    EMR
-3. Quantity: 
-    Three tissue fragments, up to 0.5x0.45x0.4 cm in size
-4. Comment: Nil
-All for section         Jar 0
-A1
-MICROSCOPIC:
-1. Histological diagnosis:
-Neoplastic polyp
-II. Serrated adenoma/polyp: 
-Sessile serrated lesion
-2. Histological grade:
-No definite dysplasia is found.
-3. Margins status (including stalk):
-Margin(s) cannot be assessed</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Sessile serrated lesion, Ascending colon, S/p EMR, 2.0cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
     <t>3y</t>
-  </si>
-  <si>
-    <t>P250690004274</t>
-  </si>
-  <si>
-    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20220819
-          Start time:    11 時  31 分 32 秒
-     Reach cecum at :    11 時  33 分 47 秒
-          End  time:     11 時  51 分 39 秒
- Clinical Diagnosis :
-   R/O colon lesion
- Indication :
-   國民健康署糞便潛血檢查陽性
- Colon preparation agent :
-   PEG-ELS類
- Cleansing time :
-   Evening single dose
- Cleansing Level :
-   Fair
- Instrument :
-   CF-H290I                     211
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   None
- Accessibility :
-   Easy
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   One 4.0cm lateral spreading tumor, granular type, at A-colon near ICV. ICV 
-   orifice can not be identified. One 0.8cm Ip polyp at A-colon. Polypectomy and 
-   hemoclip application (surclip 11mm) X 1 was done (A). One 1.2cm Ip polyp at 
-   A-colon. Polypectomy and hemoclip application (surclip 11mm) X 2 was done 
-   (B). Internal hemorrhoid was noted
- Endoscopic diagnosis :
-   Tubular adenoma,Ip,Ascending colon,0.8cm,S/p hot snare polypectomy,S/p 
-   hemoclipping,(A)
-   Tubular adenoma,Ip,Ascending colon,1.2cm,S/p hot snare polypectomy,S/p 
-   hemoclipping,(B)
-   Tubulovillous adenoma,LST-G(Laterally spreading tumor,granular 
-   type),Ascending colon,4cm,Not managed : Difficulty in management (refer to 
-   other hospital)
-   Internal hemorrhoid
- Complication :
-   NIL
- Suggestion :
-   Post polypectomy care and pursue pathology report
-     技術員:OOOO
-     檢查者:OOO                      / OOO主治醫師(台消內專科證字第OOOO號)</t>
   </si>
   <si>
     <t>PATHOLOGICAL DIAGNOSIS:
@@ -3223,26 +1632,6 @@
 c. Margin status (for high-grade dysplasia or carcinoma): not applicable
 d. Lymphovascular invasion: not applicable
 e. Perineural invasion: not applicable</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Ascending colon, S/p hot snare polypectomy, S/p hemoclipping, 0.8cm.
-B: Tubulovillous adenoma, Ascending colon, S/p hot snare polypectomy, S/p hemoclipping, 1.2cm.
-A-colon: Tubulovillous adenoma, LST-G (Laterally spreading tumor, granular type), Ascending colon, 4cm, Not managed: Difficulty in management (refer to other hospital).
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 3 (less than 10mm: 1, 10-19mm: 1, greater than or equal to 20mm: 1)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: Yes
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
   </si>
   <si>
     <t>P250690007474</t>
@@ -3480,669 +1869,6 @@
 3 Years</t>
   </si>
   <si>
-    <t>P250690011400</t>
-  </si>
-  <si>
-    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20221228
-          Start time:    10 時  52 分 57 秒
-     Reach cecum at :    10 時  56 分 32 秒
-          End  time:     11 時  39 分 53 秒
- Clinical Diagnosis :
-   Colon polyp history
- Indication :
-   瘜肉或腫瘤切除
- Colon preparation agent :
-   Phosphosoda類
- Cleansing time :
-   Split dose
- Cleansing Level :
-   Excellent
- Instrument :
-   CF-H290I                     5
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   None
- Accessibility :
-   Easy
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   The scope was inserted into cecum. There was a 2.5cm lateral spreading tumor, 
-   non-granular type, located at A-colon, sessile serrated adenoma was 
-   suspected, hot EMR was done(A), another 0.5cm 0-Is lesion closed by also 
-   resected, followed with Sure clips x4 for closure of mucosal defect(A).
-   Another two 0.8cm and 0.5cm 0-Is adenoma located at A-colon, hot EMR was 
-   performed, followed with sure clip x 1(B). Other multiple 0.5cm 0-Is adenoma 
-   distributed at A-colon and proximal T-colon also observed. There was a 1.5cm 
-   0-Isp hyperemic adenoma, located at S-colon, hot EMR was performed, followed 
-   with sure clip x 1(C).
-   (Total 5 polyps removed, 2 hot EMR and 3 hot polypectomy)
- Endoscopic diagnosis :
-   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
-   type),Ascending colon,2.5cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
-   hemoclipping,(A)
-   Tubular adenoma,Is,Ascending colon,0.8cm,S/p hot snare polypectomy,(B)
-   Tubulovillous adenoma,Isp,Sigmoid colon,1.5cm,S/p hot EMR (Endoscopic 
-   muscosal resection),S/p hemoclipping,(C)
- Complication :
-   NIL
- Suggestion :
-   Post EMR/polypectomy care
-   OPD f/u
-   freqeunt CFS for serial polypectomy
-     技術員:OOOO
-     檢查者:OOO杰                  / OOO主治醫師(台消外專科證字第OOOO號)</t>
-  </si>
-  <si>
-    <t>PATHOLOGICAL DIAGNOSIS:
-1. Large intestine, labeled "(A) A-colon", colonoscopic hot mucosal resection: hyperplastic polyp
-2. Large intestine, labeled "(B) A-colon", colonoscopic hot snare polypectomy: hyperplastic polyp
-3. Large intestine, labeled "(C) S-colon", colonoscopic hot mucosal resection: traditional sessile adenoma
-GROSS:
-Three bottles labeled as following are received:
-1. "(A) A-colon": two pieces of tan and elastic tissue fragments measuring 1.2 x 0.9 x 0.8 cm. (block A, totally submitted)
-2. "(B) A-colon": multiple pieces of tan and elastic tissue fragments measuring 0.8 x 0.6 x 0.3 cm. (block B, totally submitted)
-3. "(C) S-colon": one piece of tan and elastic tissue fragment measuring 1.0 x 0.8 x 0.6 cm. (block C, totally submitted)
-The specimens are submitted as above. 
-MICROSCOPIC FINDINGS:
-Section A:
-a. Histological diagnosis: hyperplastic polyp
-b. Histological grade: not applicable
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section B:
-a. Histological diagnosis: hyperplastic polyp
-b. Histological grade: not applicable
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-Section C:
-a. Histological diagnosis: traditional sessile adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Hyperplastic polyp, Ascending colon, S/p hot EMR, 2.5cm.
-B: Hyperplastic polyp, Ascending colon, S/p hot snare polypectomy, 0.8cm.
-C: Traditional sessile adenoma, Sigmoid colon, S/p hot EMR, 1.5cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
-  </si>
-  <si>
-    <t>P250690011599</t>
-  </si>
-  <si>
-    <t>Clinical Diagnosis                                      
-  R/O colon lesion
- Indication                                              
-  Abnormal image finding
- Colon preparation agent                                 
-  Phosphosoda 類
- Cleansing time:                                         
-  Split dose                                             
- Cleansing Level:                                        
-  Good                                                   
- Instrument:                                             
-  CF-H2901                   .2                
- Insertion level:                                        
-  Cecum                                                  
- Pre-mediction:                                          
-  Hyoscine butylbromide                                  
- Sedation                                                
-  Propofol
- Accessibility:                                          
-  Difficult                                              
- Anti-platelet/Anti-coagulant agents                     
-  Nil
- Colonoscopic Findings                                   
-  One 3.0cm lateral spreading tumor, granular, mixed nodular type was noted at 
-  A-colon. EMR and hemoclip application X 4 were done. Observation was 
-  incomplete due to specimen retrival. Internal hemorrhoid was noted
- Diagnosis                                                                       檢體總數:                     1           
-  Tubulovillous adenoma,LST-G(Laterally spreading tumor,granular type),Ascending 
-  colon,3.0cm,S/p EMR (Endoscopic mucosal resection),S/p hemoclipping,(A)
-  Internal hemorrhoid
-  Incomplete study
- Complication                                            
-  Nil
- Suggestion                                              
-  Post EMR care and pursue pathology report
-  Repeat CFS 3-6 months later</t>
-  </si>
-  <si>
-    <t>PATHOLOGICAL DIAGNOSIS:
-Colon, A-colon, EMR: tubulovillous adenoma
-GROSS:
-The specimen consists of one tissue fragment, measuring 2.8x2.5x0.7 cm in size. The entire specimen is submitted in 2 cassettes, labeled A1-2.
-MICROSCOPIC FINDINGS:
-a. Histological diagnosis: tubulovillous adenoma
-b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
-c. Margin status (for high grade dysplasia or carcinoma): not applicable
-d. Lymphovascular invasion: not applicable
-e. Perineural invasion: not applicable
-f. Comments: nil.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Tubulovillous adenoma, Ascending colon, S/p EMR and S/p hemoclipping, 3.0cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 1)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: Yes
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
-    <t>P250690011698</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-                             National Taiwan University  Hospital
-病歷號: OOOOOO
-                          大腸鏡檢查過程紀錄暨報告
-姓　名: OOO
-生　日: ____/___/___              (綜診部內視鏡中心)
-                                                                             第 1  頁
-   檢查單號:  T0174398574         年齡: 75              保險身分:   
-   檢查日期:  20180111            性別: M               流水序號:  C079130
- Examination time :Start time :  10:55:14         End time :  11:38:09
- Clinical Diagnosis :
-   Colon polyps history
- Indication :
-   Colon polyps history
- Colon preparation :
-   Niflec
- Condition :
-   Poor
- Instrument :
-   CF-Q260AL .16
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Dromucum+Rapifen+Propofol
- Cleansing time :
-   Evening
- Medication history :
-   Clopidogrel (hold 7 days)
- Colonoscopic Findings :
-   Up to cecum, much fecal material was noted at right side colon. Several small 
-   outpouching lesions were noted at cecum. Several scars were noted at hepatic 
-   flexture and transverse colon. One 1.5cm 0-IIa lesion was noted at descending 
-   colon and EPMR was done(A), followed by hemoclipping. Several 0.2cm to 0.4cm 
-   0-Is whitish polyps were noted at sigmoid colon and biopsy to one of the 
-   lesions was done(B). Internal hemorrhoid was noted.
- Endoscopic Diagnosis :
-   Diverticulosis, cecum.
-   Colon scar, hepatic flexture and transverse colon.
-   Lateral spreading tumor, non-granular type, 1.5cm, descending colon, s/p 
-   EPMR(A), s/p hemoclipping.
-   Probably hyperplastic polyps, sigmoid colon, s/p biopsy removal(B).
-   Internal hemorrhoids.
-   Poor colon preparation.
- Complication :
-   Negative
- Suggestion :
-   Post EPMR/biopsy care and pursue pathology report
- Specimens :
-   2 Bottles
-   助理:  OOO護士
- 檢查者:  OOO住院醫師          / OOO主治醫師         / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, colon, descending, colonoscopic mucosal resection, tubular adenoma
-Intestine, large, colon, sigmoid, colonoscopic biopsy, hyperplastic polyp
-MACROSCOPIC:
-A: two tissue fragments, up to 0.4 x 0.3 x 0.3 cm in size
-B: two tissue fragments, up to 0.5 x 0.2 x 0.2 cm in size
-All for section and labeled as:    Jar 0
-A: descending colon                    B: sigmoid colon
-MICROSCOPIC:
-* Histological diagnosis: 
-  A: Tubular adenoma
-  B: Hyperplastic polyp, goblet cell type 
-* High grade dysplasia (including severe dysplasia and carcinoma in situ): Absent
-* Invasive carcinoma: Absent 
-* Surgical margin: 
-  Section A: Cannot be assessed due to tissue fragmentation
-  Section B: Not applicable
-Ref: S1801695, S1635378, S9909665</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Descending colon, S/p EPMR and hemoclipping, 1.5cm.
-B: Hyperplastic polyp, Goblet cell type, Sigmoid colon, S/p biopsy and removal, 0.2-0.4cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 1, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
-    <t>P250690000707</t>
-  </si>
-  <si>
-    <t>病歷號:OOOOOOO
- 姓  名:OOO            大腸鏡檢查過程記錄暨報告
- 生  日:西元 OOOOOOOO
-                                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20190918            性別: M               流水序號:  報告流水號
-          Start time: 15  時 39 分 47 秒
-     Reach cecum at : 15  時 48 分 17 秒
-          End  time:  16  時 06 分 23 秒
- Clinical Diagnosis :
-   Susp. colonic lesion
- Indication :
-   Positive iFOBT
- Colon preparation agent :
-   PEG-ELS類
- Cleansing time :
-   Morning single dose
- Cleansing Level :
-   Good
- Instrument :
-   CF-H260AL   
- Insertion level :
-   Terminal ileum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   IVG-assist
- Accessibility :
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-       During endoscope insertion by CF-H260AZI, one sharp angle was faced at 
-   S-D junction, 35cm above anal verge. It's difficult to pass through. We 
-   changed the endoscope to CF-H260AL for further survey. Up to cecum, some 
-   fecal material was noted inside the colon. One 0.2cm 0-Is polyp was noted at 
-   cecum and biopsy removal was done(A). 
-       One nongranular laterally spreading tumor, &gt; 2.0cm, over the fold, was 
-   found at ascending colon. To be snaring was difficult due to large size and 
-   poor approaching angle.
-       One 0.6cm 0-IIa polyp was found at sigmoid colon and cold snaring 
-   polypectomy was done(B). Mixed hemorrhoid was found.
- Endoscopic diagnosis :
-   Inflammatory polyp,Is,Cecum,0.2cm,S/p biopsy and removal,(A)
-   Sessile serrated adenoma,IIa,Sigmoid colon,0.6cm,S/P cold Snaring 
-   polypectomy,(B)
-   Sessile serrated adenoma,LST-NG(Laterally spreading tumor,non-granular 
-   type),Ascending colon,2.0cm,Not managed : Difficulty in management (refer to 
-   other hospital)
-   Mixed hemorrhoids
- Complication :
-   NIL
- Suggestion :
-   Pursue the pathology report
-   Post-polypectomy care
-   Suggest hospital transfer for ESD to deal with large LST-NG at ascending 
-   colon
-   助理:   
- 檢查者:                          /                       /OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, cecum, labeled as A, colonoscopic biopsy, tubular adenoma
-Intestine, large, colon, sigmoid, labeled as B, colonoscopic polypectomy, hyperplastic polyp
-Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
-MACROSCOPIC:
-1. Lesion site: 
-    A: Cecum       B: Sigmoid
-2. Specimen type: 
-    A: Biopsy      B: Polypectomy 
-3. Quantity: 
-    A: One tissue fragment, 0.2 x 0.15 x 0.15 cm in size
-    B: One tissue fragment, 0.5 x 0.2 x 0.15 cm in size
-4. Comment: Nil
-All for section and labeled as:                 Jar 0
-    A: Cecum       B: Sigmoid
-MICROSCOPIC:
-1. Histological diagnosis:
-Neoplastic polyp
-I. Adenoma: 
-    A: Tubular adenoma 
-2. Histological grade:
-    A: Low grade dysplasia (including mild and moderate dysplasia)
-3. Margins status (including stalk):
-    A: Not applicable.
-4. Comment: 
-    The section B shows a hyperplastic polyp.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Cecum, S/p biopsy and removal, 0.2cm.
-B: Hyperplastic polyp, Sigmoid, S/p cold Snaring polypectomy, 0.6cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 1 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-7-10 Years</t>
-  </si>
-  <si>
-    <t>P250690000997</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
-病歷號:OOOOOOOO             National Taiwan University  Hospital
-姓　名: OOO
-                          大腸鏡檢查過程紀錄暨報告
-生　日: OOOOOOOO                                                             第 1  頁
-   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
-   檢查日期:  20200330            性別: F               流水序號:  報告流水號
- Examination time :Start time :                   End time :   
- Clinical Diagnosis :
-   Susp. colonic lesion
- Indication :
-   Positive FOBT
- Colon preparation :
-   Niflec
- Condition :
-   Fair
- Instrument :
-   CF-H260AL  
- Insertion level :
-   Cecum
- Pre-medication :
-   Buscopan
- Anesthesia :
-   Nil
- Cleansing time :
-   Morning
- Medication history :
-   Nil
- Colonoscopic Findings :
-   Up to cecum, some fecal material was noted inside the colon. One 
-   0.4cm 0-IIa polyp and one 0.5cm 0-IIa polyp were found at cecum. Cold 
-   snaring polypectomy with following hemoclipping(x1) as wound closure 
-   was done(A). 
-   One 1.2cm granular laterally spreading tumor was noted at cecum, 
-   behind the fold. EPMR after glycerol injection was done and following biopsy 
-   removal was also performed to remove suspicious residual part. Hemoclipping
-   (x4) as wound closure was done(B). Internal hemorrhoid was found. 
- Endoscopic Diagnosis :
-   1.Cecal polyps(x2), suspected tubular adenomas, status post cold 
-   snaring polypectomy(A)
-   2.Cecal LST-G, susected tubular adenoma, status post EPMR and biopsy 
-   removal(B)
-   3.Internal hemorrhoid
- Complication :
-   Negative
- Suggestion :
-   Pursue the pathology report
-   Post-EPMR care
-   Repeat CFS 3 months later for post-EPMR follow-up
- Specimens :
-   2 Bottles
-   助理:   
- 檢查者:                          /                        / OOO主治醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, cecum, labeled as A, colonoscopic polypectomy, (1)tubular adenoma; (2)sessile serrated adenoma
-Intestine, large, cecum, labeled as B, colonoscopic piecemeal mucosal resection, hyperplastic polyp 
-Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
-MACROSCOPIC:
-1. Lesion site: 
-    A: Cecum      B: Cecum
-2. Specimen type: 
-    A: Polypectomy      B: Endoscopic piecemeal mucosal resection
-3. Quantity: 
-    A: Two tissue fragments, up to 1.5 x 0.8 x 0.1 cm in size
-    B: Six tissue fragments, up to 0.6 x 0.3 x 0.3 cm in size
-4. Comment: Nil
-All for section and labeled as:                 Jar 0
-    A: Cecum      B: Cecum
-MICROSCOPIC:
-1. Histological diagnosis:
-Neoplastic polyp
-I. Adenoma: 
-    A: Tubular adenoma 
-II. Serrated adenoma/polyp: 
-    A: Sessile serrated adenoma/polyp  
-2. Histological grade:
-    A: Low grade dysplasia (including mild and moderate dysplasia)
-3. Margins status (including stalk):
-    A: Margin cannot be assessed.
-4. Comment: 
-    The section A shows a tubular adenoma and a sessile serrated adenoma, respectively.
-    The section B shows a hyperplastic polyp with chronic inflammation and focal regenerative atypia.</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-Here are the integrated labels:
-A: Tubular adenoma, Sessile serrated adenoma, Cecum, S/p cold snaring polypectomy with hemoclipping, 0.4cm.
-B: Hyperplastic polyp, Cecum, S/p EPMR and biopsy removal, 1.2cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 1 (less than 10mm: 1, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
-  </si>
-  <si>
-    <t>P250690002089</t>
-  </si>
-  <si>
-    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
- 病歷號:  OOOOOO                    National Taiwan University  Hospital
-                                 大腸鏡檢查過程記錄暨報告
- 姓　名:  OOO
-                                           (內視鏡中心)
- 生　日:  ____/___/___                                                                              第 1    頁
-     檢查單號:    T0122661861              年齡:   66                 保險身分:     
-     檢查日期:    20120510                 性別:   F                  流水序號:     C011808
- Examintion time :      Start time :      13:52:38            End time :      14:14:27
- Clinical Diagnosis :
-    Colon cancer operated FU
- Indication :
-    Colon cancer operated FU
- Colon preparation :
-    Niflec
- Condition :
-    Good
- Instrument :
-    CF-Q260AI     
- Insertion level :
-    Cecum
- Pre-medication :
-    Buscopan
- Anesthesia :
-    Dromucum+Rapifen+Propofol
- Cleansing time :
-    Morning
- Medication history :
-    Nil
- Colonoscopic Findings :
-    Hyperemic mucosal lesion with nodular surface and fragile mucosa was noted 
-    over recto-vaginal area. Biopsy was done. Mixed hemorrhoid was noted. Status 
-    post lowere anterior resection with anastomosis scar was noted.
- Endoscopic Diagnosis :
-    Inflammatory polyp, LST, 3.0 cm, rectal pouch, s/p biopsy
-    Mixed hemorrhoid
-    Status post lower anterior resection with anastomosis scar
- Complication :
-    Negative
- Suggestion :
-    Nil
- Specimens :
-    One bottle 
-  Assistant :  OOO              Examiner :   OOO      醫師 /             醫師 / OOO      醫師</t>
-  </si>
-  <si>
-    <t>Intestine, large, colon, status post low anterior resection, retrovaginal area, endoscopic biopsy, ulcer
-       The specimen submitted consists of 4 tissue fragments measuring up to 0.4 x 0.3 x 0.1 cm in size fixed in formalin.
-       Grossly, they are brownish and soft.        
-        All for section.                                                Jar 0 
-        Microscopically, it shows ulceration with granulation tissue and dense mixed inflammatory cell infiltration.
-Ref: 
-S1140891 Intestine,large,colon, previous resection margin, status post resection, endoscopic biopsy, ulcer
-S1027803 Skin, subcutis, T-colostomy, closure, chronic inflammation, suture granuloma
-S1014359 Soft tissue, pelvic, labeled as "recto-vaginal fistula", fistulectomy, compatible with fistula
-S0940926
-(01). Intestine,large,rectum, resection, adenocarcinoma
-(02). Lymph node, regional, lymphadenectomy, no evidence of metastasis, (0/11)</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Inflammatory polyp, Rectal pouch, S/p biopsy, 3.0cm.
-B: Mixed hemorrhoid, Rectal pouch, S/p biopsy, (no size mentioned)
-C: Status post lower anterior resection with anastomosis scar, Rectal pouch, S/p procedure, (no size mentioned)
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3-5 Years</t>
-  </si>
-  <si>
-    <t>P250690001103</t>
-  </si>
-  <si>
-    <t>"國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
-                                                   National Taiwan University Hospital  Hsin-Chu Hospital
- 病歷號: OOOOOOO
- 姓  名: OOO
-                                 大腸鏡檢查過程紀錄暨報告
- 生  日: OOOOOOOO
-檢查單號: OOOOOOOOO        年齡:OO          性別: F         檢查日期: 20230712
-          Start time:    13 時  51 分 14 秒
-     Reach cecum at :    13 時  53 分 42 秒
-          End  time:     14 時  01 分 37 秒
- Clinical Diagnosis :
-   Hemorrhoid
- Indication :
-   Bloody stool
- Colon preparation agent :
-   Phosphosoda類
- Cleansing time :
-   Split dose
- Cleansing Level :
-   Excellent
- Instrument :
-   CF-H290I                     H8
- Insertion level :
-   Cecum
- Pre-medication :
-   Hyoscine butylbromide
- Sedation :
-   Midazolam (Dormicum)
-   Propofol
-   Fentanyl (含Alfentanyl)
- Accessibility :
-   Easy
- Anti-platelet / Anti-coagulant agents :
-   NIL
- Colonoscopic Findings :
-   The scope was inserted into cecum. There was a 1.5cm granular type lateral 
-   spreading tumor (LST-G), r/o sessile serrated adenoma, located within cecum, 
-   piecemeal cold snare polypectomy was done(A). Mixed hemorrhoidds were also 
-   noted.
- Endoscopic diagnosis :
-   Sessile serrated lesion(SSL),LST-G(Laterally spreading tumor,granular 
-   type),Cecum,1.5cm,S/p cold snare polypectomy,(A)
-   Mixed hemorrhoids
- Complication :
-   NIL
- Suggestion :
-   post polypectomy care, f/u
- 技術員:OOO
- 檢查者:OOO       / 住院醫師:          OOO主治醫師:OOO主治醫師(台消外專科證字第OOOO號)"</t>
-  </si>
-  <si>
-    <t>Intestine, large, cecum, endoscopic polypectomy, sessile serrated lesion
-[Gross examination]
-1. Specimen size: three, up to 1.0 x 0.8 x 0.1 cm 
-2. Tissue origin: cecum
-3. Gross description: tan and elastic
-  All for sections. Jar 0 
-[Microscopic description]
-1. Histological diagnosis: sessile serrated lesion
-2. High-grade dysplasia or invasive carcinoma: absent
-3. Margin: cannot be assessed
-Ref:
-新竹 H2204227</t>
-  </si>
-  <si>
-    <t>1. Original Report:
-------------------------------------------------------------
-A: Sessile serrated lesion, Cecum, S/p cold snare polypectomy, 1.5cm.
-------------------------------------------------------------
-2. Clinical Findings Summary:
-------------------------------------------------------------
-Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
-Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
-High-Risk Features:
-  - High-Grade Dysplasia (HGD): No
-  - Villous Features: No
-  - Piecemeal Resection: No
-------------------------------------------------------------
-3. 2020 USMSTF recommendation interval
-3 Years</t>
-  </si>
-  <si>
     <t>病歷號: OOOOOOO
  姓  名:OOO             大腸鏡檢查過程紀錄暨報告
  生  日:西元 OOOOOOO
@@ -4217,12 +1943,2324 @@
   <si>
     <t>id</t>
   </si>
+  <si>
+    <t>P250690001338</t>
+  </si>
+  <si>
+    <t>"Clinical Diagnosis                                      
+  Colon polyps
+ Indication                                              
+  Colon polyps
+ Colon preparation agent                                 
+  PEG-ELS 類
+ Cleansing time:                                         
+  Morning single dose                                    
+ Cleansing Level:                                        
+  Good                                                   
+ Instrument:                                             
+  CF-Q260AL                  .22               
+ Insertion level:                                        
+  Cecum                                                  
+ Pre-mediction:                                          
+  Hyoscine butylbromide                                  
+ Sedation                                                
+  Propofol
+  Fentanyl(含Alfentanyl)
+  其他鎮靜麻醉藥物
+ Accessibility:                                          
+  Easy                                                   
+ Anti-platelet/Anti-coagulant agents                     
+  Clopidogrel(Plavix)   Hold 5 days
+ Colonoscopic Findings                                   
+  Up to cecum, some fecal materials were noted in the colon.  One 1.5cm LST-NG 
+  type polyp was noted at A-colon, s/p EMR and hemoclipping x 4 (A). One 1.0cm 
+  0-Is polyp was noted at proximal T-colon, s/p EMR and hemoclipping x 1 (B). 
+  One 0.6cm 0-Is polyp was noted at S-colon, s/p polypectomy and hemoclipping x 
+  1 (C). Internal hemorrhoid was noted. 
+ Diagnosis                                                                       檢體總數:                     3           
+  Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular type),Ascending 
+  colon,1.5cm,S/p EMR (Endoscopic mucosal resection),S/p hemoclipping,(A)
+  Tubular adenoma,ls,Transverse colon,1.0cm,S/p EMR (Endoscopic mucosal 
+  resection),S/p hemoclipping,(B)
+  Tubular adenoma,ls,Sigmoid colon,0.6cm,S/p polypectomy,S/p hemoclipping,(C)
+  Internal hemorrhoid
+ Complication                                            
+  Negative
+ Suggestion                                              
+  Post EMR care and pursue pathology report"</t>
+  </si>
+  <si>
+    <t>"1. Original Report:
+------------------------------------------------------------
+A: Sessile serrated polyp, A-colon, S/p EMR, 1.5cm.
+B: Tubular adenoma, T-colon, S/p EMR, 1.0cm.
+C: Tubular adenoma, S-colon, S/p polypectomy, 0.6cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years"</t>
+  </si>
+  <si>
+    <t>P250690001360</t>
+  </si>
+  <si>
+    <t>病歷號: OOOOOOO
+ 姓  名:OOO             大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOO         年齡: 47              保險身分:   
+   檢查日期:  20240522            性別: M               流水序號:  報告流水號
+          Start time:    13 時  29 分 49 秒
+     Reach cecum at :    13 時  33 分 12 秒
+          End  time:     14 時  53 分 53 秒
+ Clinical Diagnosis :
+   Post polypectomy surveillance
+ Indication :
+   Post polypectomy surveillance
+ Colon preparation agent :
+   Magnesium citrate類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Fair
+ Instrument :
+   CF212                         
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Easy
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   One 2.0 cm IIa NICE type 1 lesion was noted at the A-colon S/p hot EMR and 
+   hemoclipping (A). One 1.5 cm IIa NICE type 1 lesion was noted at the A-colon 
+   S/p hot EMR and hemoclipping (B). One 0.3 cm Is NICE type 2 lesion was noted 
+   at the A-colon S/p CSP (C). One 0.3 cm IIa NICE type 1 lesion was noted at 
+   the A-colon S/p CSP (D). One 0.3 cm IIa NICE type 1 lesion was noted at the 
+   T-colon S/p CSP (E). One 1.2 cm IIa NICE type 1 lesion was noted at the D-
+   colon S/p hot EMR and hemoclipping (F). One 0.3 cm IIa NICE type 2 lesion was 
+   noted at the S-colon S/p CSP (G). One 0.4 cm IIa NICE type 2 lesion was noted 
+   at the S-colon S/p CSP (H).
+ Endoscopic diagnosis :
+   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
+   type),Ascending colon,2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(A)
+   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
+   type),Ascending colon,1.5cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(B)
+   Tubular adenoma,Is,Ascending colon,0.3cm,S/p cold snare polypectomy,(C)
+   Hyperplastic polyp,IIa,Ascending colon,0.3cm,S/p cold snare polypectomy,(D)
+   Hyperplastic polyp,IIa,Transverse colon,0.3cm,S/p cold snare polypectomy,(E)
+   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
+   type),Descending colon,1.2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(F)
+   Tubular adenoma,IIa,Sigmoid colon,0.3cm,S/p cold snare polypectomy,(G)
+   Tubular adenoma,IIa,Sigmoid colon,0.4cm,S/p cold snare polypectomy,(H)
+   Mixed hemorrhoids
+ Complication :
+   NIL
+ Suggestion :
+     技術員: OOO
+     檢查者:                         / OOO主治醫師</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+Intestine, large, ascending, labeled A, endoscopic mucosal resection --- sessile serrated lesion
+Intestine, large, ascending, labeled B, endoscopic mucosal resection --- sessile serrated lesion
+Intestine, large, ascending, labeled C, colonoscopic polypectomy --- tubular adenoma
+Intestine, large, ascending, labeled D, colonoscopic polypectomy --- tubular adenoma
+Intestine, large, transverse, labeled E, colonoscopic polypectomy --- mucosal polyp
+Intestine, large, descending, labeled F, endoscopic mucosal resection --- sessile serrated lesion
+Intestine, large, sigmoid, labeled G, colonoscopic polypectomy --- tubular adenoma
+Intestine, large, sigmoid, labeled H, colonoscopic polypectomy --- sessile serrated lesion
+GROSS FINDINGS:
+The specimen A submitted consists of a tissue fragment measuring 1.6 x 1.6 x 0.8 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic.
+All for section and labeled as A.
+The specimen B submitted consists of a tissue fragment measuring 1.5 x 1.3 x 0.9 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic.
+All for section and labeled as B.
+The specimen C submitted consists of 2 tissue fragments measuring 0.3 x 0.2 x 0.1 cm and 0.3 x 0.1 x 0.1 cm in size, fixed in formalin.
+Grossly, they are tan and elastic.
+All for section and labeled as C.
+The specimen D submitted consists of a tissue fragment measuring 0.7 x 0.3 x 0.2 cm in size, fixed in formalin.
+Grossly, it is tan and elastic.
+All for section and labeled as D.
+The specimen E submitted consists of a tissue fragment measuring 0.6 x 0.4 x 0.3 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic.
+All for section and labeled as E.
+The specimen F submitted consists of a tissue fragment measuring 1.3 x 0.6 x 0.4 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic.
+All for section and labeled as F.
+The specimen G submitted consists of a tissue fragment measuring 0.4 x 0.2 x 0.1 cm in size, fixed in formalin.
+Grossly, it is tan and elastic.
+All for section and labeled as G.
+The specimen H submitted consists of a tissue fragment measuring 0.9 x 0.6 x 0.1 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic.
+All for section and labeled as H.
+MICROSCOPIC FINDINGS:
+Specimen A:
+Sections show a picture of sessile serrated lesion, which is composed of irregular indentation of neoplastic epithelium containing slightly enlarged and hyperchromatic nuclei. The lateral resection margin is involved by the lesion, and the deep margin is free.
+Specimen B:
+Sections show a picture of sessile serrated lesion, which is composed of irregular indentation of neoplastic epithelium containing slightly enlarged and hyperchromatic nuclei. The resection margin is uninvolved.
+Specimen C:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen D:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen E:
+a. Histological diagnosis: mucosal polyp
+b. Histological grade: not applicable
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen F:
+Sections show a picture of sessile serrated lesion, which is composed of irregular indentation of neoplastic epithelium containing slightly enlarged and hyperchromatic nuclei. The resection margin is uninvolved.
+Specimen G:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen H:
+Sections show a picture of sessile serrated lesion, which is composed of irregular indentation of neoplastic epithelium containing slightly enlarged and hyperchromatic nuclei. The resection margin cannot be evaluated due to poor orientation of the specimen.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Sessile serrated lesion, Ascending colon, S/p hot EMR, 2cm.
+B: Sessile serrated lesion, Ascending colon, S/p hot EMR, 1.5cm.
+C: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.3cm, Low-grade dysplasia.
+D: Hyperplastic polyp, Ascending colon, S/p cold snare polypectomy, 0.3cm.
+E: Hyperplastic polyp, Transverse colon, S/p cold snare polypectomy, 0.3cm.
+F: Sessile serrated lesion, Descending colon, S/p hot EMR, 1.2cm.
+G: Tubular adenoma, Sigmoid colon, S/p cold snare polypectomy, 0.3cm, Low-grade dysplasia.
+H: Sessile serrated lesion, Sigmoid colon, S/p cold snare polypectomy, 0.4cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 2, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 4 (less than 10mm: 1, greater than or equal to 10mm: 3)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690000741</t>
+  </si>
+  <si>
+    <t>病歷號: OOOOOOO
+ 姓  名:OOO             大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOO         年齡: 80              保險身分:   
+   檢查日期:  20230503            性別: M               流水序號:  報告流水號
+          Start time:    10 時  31 分 37 秒
+     Reach cecum at :    10 時  49 分 50 秒
+          End  time:     11 時  07 分 01 秒
+ Clinical Diagnosis :
+   colon polyp
+ Indication :
+   Bowel habitus change
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Poor
+ Instrument :
+   CF-H290I                     201
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Buscopan
+ Sedation :
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Easy
+ Anti-platelet / Anti-coagulant agents (Hold :     Days)
+   NIL
+ Colonoscopic Findings :
+   The scope was inserted to cecum. One 2.0cm lateral spreading tumor 
+   non-granular type was noted at T-colon, s/p endoscopic mucosal resection, s/p 
+   hemoclipping x 2(A). Mixed hrmorrhoid was seen.
+ Endoscopic diagnosis :
+   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
+   type),Transverse colon,2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(A)
+   Mixed hemorrhoids
+ Complication :
+   NIL
+ Suggestion :
+   Post EMR care and pursue pathology report
+   F/U CFS 1 year later
+     技術員: OOO
+     檢查者:                         / OOO主治醫師(台消內鏡專科證字第OOOOOO號)</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+Intestine, large, transverse, endoscopic mucosal resection --- sessile serrated lesion
+GROSS FINDINGS:
+The specimen submitted consists of a tissue fragment measuring 1.7 x 0.9 x 0.8 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic.
+All for section.
+MICROSCOPIC FINDINGS:
+Sections show a picture of sessile serrated lesion, which is composed of irregular indentation of neoplastic epithelium containing slightly enlarged and hyperchromatic nuclei. The resection margin is uninvolved.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Sessile serrated lesion, Transverse colon, S/p hot EMR, 2cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690001580</t>
+  </si>
+  <si>
+    <t>國 立 台 灣 大 學 醫 學 院 附 設 醫 院
+ 病歷號:OOOOOOO            National Taiwan University Hospital 
+ 姓  名:OOO           大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOO           (綜診部內視鏡中心)                           第 1  頁
+   檢查單號:  OOOOOO         年齡: 60              保險身分:   
+   檢查日期:  OOOOOO            性別: M               流水序號:  OOOOOO
+          Start time:    17 時  06 分 09 秒
+     Reach cecum at :    17 時  12 分 42 秒
+          End  time:     17 時  55 分 26 秒
+ Clinical Diagnosis :
+   For polypectomy
+ Indication :
+   For polypectomy
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Good
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Instrument :
+   CF H290I.1
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Fair
+ Colonoscopic Findings :
+   The scope was inserted to the cecum smoothly. A 2 cm NICE type 2 lateral 
+   spreading tumor with homogeneous nodularity was noted over cecum. A Hot EMR 
+   was performed and the specimens were labeled as A. A hemoclips was used for 
+   hemostasis. nother 0.5 cm NICE type 2 polypoid lesion was noted over cecum. 
+   Cold snare polypectomy was performed and the specimen was labeled as B.
+    A 0.2 cm NICE type 2 polypoid lesion was noted over ascending colon. Cold 
+   snare polypectomy was performed and the specimen was labeled as C. A 0.2 cm 
+   NICE type 2 lesion was noted over ascending colon. Cold snare polypectomy was 
+   performed and the specimen was labeled as D. Diverticulae were noted over 
+   ascending colon and sigmoid colon. External hemorrhoid was noted. 
+ Endoscopic diagnosis :
+   Tubular adenoma,LST-G(Laterally spreading tumor,granular type),Cecum,2cm,S/p 
+   hot EMR (Endoscopic muscosal resection),S/p hemostasis,S/p hemoclipping,(A)
+   Tubular adenoma,Isp,Cecum,0.5cm,S/p cold snare polypectomy,(B)
+   Tubular adenoma,IIa,Cecum,0.2cm,S/p cold snare polypectomy,(C)
+   Tubular adenoma,IIa,Ascending colon,0.2cm,S/p cold snare polypectomy,(D)
+   Colonic diverticulosis,Ascending colon,Sigmoid colon
+   External hemorrhoids
+ Specimens :
+   4    bottle(s)
+ Complication :
+   NIL
+ Suggestion :
+   General surgeon OPD follow-up
+   Post EMR care and pursue pathology report
+   Avoid heavy lifting for one week
+   watch out bleeding sign
+   助理:  OOO護理師
+ 檢查者:  OOO住院醫師           /                        / OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Intestine, large, cecum, specimen A, colonoscopic mucosal resection, tubular adenoma
+Intestine, large, cecum, specimen B, colonoscopic polypectomy, tubular adenoma
+Intestine, large, cecum, specimen C, colonoscopic polypectomy, mucosal tag
+Intestine, large, colon, ascending, specimen D, colonoscopic polypectomy, mucosal tag  
+MACROSCOPIC:
+Specimen A: 3 tissue fragments, up to 1.5 x 0.5 x 0.2 cm in size
+Specimen B: 3 tissue fragments, up to 0.5 x 0.3 x 0.2 cm in size
+Specimen C: 1 tissue fragment, 0.5 x 0.3 x 0.1 cm in size
+Specimen D: 1 tissue fragment, 0.6 x 0.3 x 0.2 cm in size
+All for section and labeled as:               Jar 0
+A1-2: cecum                               B1: cecum
+C1: cecum                                 D1: ascending colon
+MICROSCOPIC:
+* Histological diagnosis: 
+  Specimen A and B: Tubular adenoma
+  Specimen C and D: Mucosal tag
+* High-grade dysplasia (including severe dysplasia and carcinoma in situ): Absent
+* Surgical margin: 
+  Specimen A: Lateral margin focally involved 
+  Specimen B: Cannot be assessed due to tangential cut
+  Specimen C and D: Not applicable</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Cecum, S/p hot EMR, 2cm.
+B: Tubular adenoma, Cecum, S/p cold snare polypectomy, 0.5cm.
+C: Mucosal tag, Cecum, S/p cold snare polypectomy, 0.2cm.
+D: Mucosal tag, Ascending colon, S/p cold snare polypectomy, 0.2cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 1)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690001643</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+Intestine, large, transverse, labeled A, colonoscopic polypectomy --- tubular adenoma
+Intestine, large, descending, labeled B, endoscopic mucosal resection --- tubular adenoma
+Intestine, large, sigmoid, labeled C, colonoscopic polypectomy --- tubular adenoma
+GROSS FINDINGS:
+The specimen A submitted consists of 2 tissue fragments measuring 0.5 x 0.3 x 0.2 cm and 0.2 x 0.2 x 0.1 cm in size, fixed in formalin.
+Grossly, they are tan and elastic. 
+All for section and labeled as A.
+The specimen B submitted consists of a tissue fragment measuring 2.0 x 1.2 x 0.2 cm in size, fixed in formalin.
+Grossly, it is tan and elastic. 
+All for section and labeled as B.
+The specimen C submitted consists of a tissue fragment measuring 0.6 x 0.2 x 0.1 cm in size, fixed in formalin.
+Grossly, it is tan and elastic. 
+All for section and labeled as C.
+MICROSCOPIC FINDINGS:
+Specimen A:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen B:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen C:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable</t>
+  </si>
+  <si>
+    <t>P250690002203</t>
+  </si>
+  <si>
+    <t>Starting time : 10時36分04秒
+   Reach time : 10時39分47秒
+   End time : 10時50分16秒
+Clinical Diagnosis : 
+      Abnormal image finding
+Indication : 
+      Abnormal image finding
+Colon preparation agent : 
+      PEG-ELS類
+Cleansing Time :       Morning single dose
+Cleansing Level :       Good
+Instrument :       CF-H290I 9 
+Insertion Level :       Cecum
+Pre-Medication :       Hyoscine butylbromide
+Sedation : 
+      IVGA
+Accessibility :       Easy
+Anti-platelet/Anti-coagulant agents : 
+      none
+Colonoscopic Findings : 
+      One 1.2cm LST-NG at cecum, s/p CSP(A)
+      One 0.6cm IIa polyp at S-colon, s/p CSP(B)
+      Internal hemorrhoid
+Endoscopic Diagnosis : 
+      Tubular adenoma, LST-NG(Laterally spreading tumor,non-granular type) ; Cecum ; 1.2 cm ; S/p cold snare polypectomy ; (A)
+      Tubular adenoma, IIa ; Sigmoid colon ; 0.6 cm ; S/p cold snare polypectomy ; (B)
+      Internal hemorrhoid
+Complication : 
+      Nil
+Suggestion : 
+      Nil
+助理檢查人員 :   OOO
+醫師科別 :    消化腸胃系內科</t>
+  </si>
+  <si>
+    <t>Intestine, large, cecum, colonoscopic cold snare polypectomy, tubular adenoma
+Intestine, large, sigmoid, colonoscopic cold snare polypectomy, tubular adenoma
+MACROSCOPIC:
+A: One tissue fragment, 0.4 x 0.3 x 0.3 cm in size 
+B: One tissue fragment, 0.5 x 0.3 x 0.2 cm in size
+All for section and labeled as:                                       Jar 0
+A: cecum
+B: sigmoid
+MICROSCOPIC:
+* Histological diagnosis:
+     A: Tubular adenoma
+     B: Tubular adenoma
+* High grade dysplasia (including severe dysplasia and carcinoma in situ): Absent 
+* Invasive carcinoma: Absent  
+* Surgical margin: 
+     Section A: Cannot be assessed 
+     Section B: Cannot be assessed 
+Ref:
+總院 S2110067
+[01]. Stomach, lesser curvature, subtotal gastrectomy, gastrointestinal stromal tumor, WHO group: Prognostic group 2, chronic gastritis, with Helicobacter infection
+[02]. Lymph node, regional, subtotal gastrectomy, negative for malignancy, (number: 3)
+[03]. Lymph node, group 1&amp;3, lymphadenectomy, negative for malignancy, (number: 4)
+總院 S2059286
+[01]. Stomach, cardia, endoscopic biopsy, chronic gastritis, with Helicobacter infection
+總院 S1832893
+[01]. Liver, S2 segment, robotic segmentectomy, cholangiocarcinoma
+[02]. Stomach, partial, partial gastrectomy, gastrointestinal stromal cell tumor, WHO prognostic group 1
+[03]. Lymph node, group 1, dissection, reactive lymphoid hyperplasia, (0/5)
+[04]. Lymph node, group 8, dissection, reactive lymphoid hyperplasia, (0/5)
+總院 S1827772
+[01]. Liver, segment 2, biopsy, cholangiocarcinoma
+癌醫 P2308751</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Tubular adenoma, Cecum, S/p cold snare polypectomy, 1.2cm.
+B: Tubular adenoma, Sigmoid colon, S/p cold snare polypectomy, 0.6cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690002239</t>
+  </si>
+  <si>
+    <t>病歷號:OOOOOOO
+ 姓  名:OOO            大腸鏡檢查過程記錄暨報告
+ 生  日:西元 OOOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
+   檢查日期:  20180420            性別: M               流水序號:  報告流水號
+          Start time: 10  時 44 分 58 秒
+     Reach cecum at : 10  時 50 分 55 秒
+          End  time:  11  時 53 分 31 秒
+ Clinical Diagnosis :
+   Susp. colonic lesions
+ Indication :
+   Positive iFOBT
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Morning single dose
+ Cleansing Level :
+   Fair
+ Instrument :
+   CF-Q260AL   
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   Nil
+ Accessibility :
+   Nil
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   Up to cecum, some fecal material was noted inside the colon. One 0.3cm 0-Is 
+   polyp was noted at ascending colon and biopsy removal was done(A). One 1.0cm 
+   nongranular laterally spreading tumor was noted at ascending colon and EMR 
+   after glycerol injection with following hemoclipping(x2) as wound closure was 
+   done(B). One 0.6cn 0-Is polyp was noted at transverse colon and polypectomy 
+   by cold snaring was done. The speciman was lost into fecal fluid. One 1.2cm 
+   nongranular laterally spreading tumor was noted at transverse colon and EMR 
+   after glycerol injection with following hemoclipping(x3) as wound closure was 
+   done(C). 
+   Some ulcers were noted at descending colon and biopsy was done(D).
+   One 0.4cm 0-IIa polyp was noted at descending colon and biopsy removal was 
+   done(E). One 1.2cm nongranular laterally spreading tumor was noted at sigmoid 
+   colon and EMR after glycerol injection with following hemoclipping(x2) as 
+   wound closure was done(F). One 0.3cm 0-Is polyp was noted at rectum and 
+   biopsy removal was done(G).  
+ Endoscopic diagnosis :
+   Tubular adenoma,Is,Ascending colon,0.3cm,S/p biopsy and removal,(A)
+   Sessile serrated adenoma,LST-NG(Laterally spreading tumor,non-granular 
+   type),Ascending colon,1.0cm,S/p EMR (Endoscopic mucosal resection),(B)
+   Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular 
+   type),Transverse colon,1.2cm,S/p EMR (Endoscopic mucosal resection),(c)
+   Colonic ulcer,Descending colon,S/p biopsy,(D)
+   Tubular adenoma,IIa,Descending colon,0.4cm,S/p biopsy and removal,(E)
+   Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular type),Sigmoid 
+   colon,1.4cm,S/p EMR (Endoscopic mucosal resection),(F)
+   Tubular adenoma,Is,Rectum,0.3cm,S/p biopsy and removal,(G)
+   Tubular adenoma,Is,Transverse colon,0.6cm,S/P cold Snaring polypectomy,(lost)
+   Internal hemorrhoid
+ Complication :
+   NIL
+ Suggestion :
+   Pursue the pathology report
+   Post-EMR care
+   Suggest regular CFS follow-up
+   助理:   
+ 檢查者:                          /                       /OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Ascending colon polyp, labeled as A, biopsy removal: tubular adenoma 
+Ascending colon polyp, labeled as B, EMR: tubular adenoma with free margin
+Transverse colon polyp, labeled as C, EMR: tubular adenoma with free margin
+Descending colon ulcer, labeled as D, biopsy: ulcer with focal adenomatous mucosa
+Descending colon polyp, labeled as E, biopsy removal: tubular adenoma 
+Sigmoid colon polyp, labeled as F, EMR: tubular adenoma with free margin
+Rectal polyp, labeled as G, biopsy removal: tubular adenoma   
+Colon Neoplastic polyp checklists
+2013/07/19病理部品管會議通過第一版
+MACROSCOPIC :
+1.	Lesion site : 
+A and B: Ascending colon
+C: Transverse colon
+D and E: Descending colon
+F: Sigmoid
+G: Rectum
+2.	Specimen type : 
+A, D and G: Biopsy
+B, C and F: Mucosal resection
+3.	Quantity: 
+The specimen A submitted consists of 2 tissue fragments measuring 0.2-0.2 cm in formalin. Total tissue is submitted in cassette A.
+The specimen B submitted consists of 2 tissue fragments measuring 0.2-0.8 cm fixed in formalin. Total tissue is submitted in cassette B.
+The specimen C submitted consists of 1 tissue fragment measuring 1x0.3x0.2 cm fixed in formalin. Total tissue is submitted in cassette C.
+The specimen D submitted consists of 2 tissue fragments measuring 0.2-0.3 cm in formalin. Total tissue is submitted in cassette D.
+The specimen E submitted consists of 1 tissue fragment measuring 0.4 cm fixed in formalin. Total tissue is submitted in cassette E.
+The specimen F submitted consists of 1 tissue fragment measuring 1x0.3 cm fixed in formalin. Total tissue is submitted in cassette F.
+The specimen G submitted consists of 3 tissue fragments measuring 0.1-0.2 cm in formalin. Total tissue is submitted in cassette G.
+MICROSCOPIC:
+1.	Histological diagnosis:
+Neoplastic polyp
+I.	Adenoma: 
+All except D: Tubular adenoma 
+2.	Histological grade:
+All except D: Low grade dysplasia (including mild and moderate dysplasia)
+3.	*Margins status ( including stalk):
+B, C and F: Margin(s) uninvolved by tumor.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ascending colon, S/p biopsy and removal, 0.3cm.
+B: Tubular adenoma, Ascending colon, S/p EMR, 1.0cm.
+C: Tubular adenoma, Transverse colon, S/p EMR, 1.2cm.
+D: Colonic ulcer with focal adenomatous mucosa, Descending colon, S/p biopsy, (no size mentioned).
+E: Tubular adenoma, Descending colon, S/p biopsy and removal, 0.4cm.
+F: Tubular adenoma, Sigmoid colon, S/p EMR, 1.2cm.
+G: Tubular adenoma, Rectum, S/p biopsy and removal, 0.3cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 6 (less than 10mm: 3, 10-19mm: 3, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690002789</t>
+  </si>
+  <si>
+    <t>Clinical Diagnosis                                      
+  Inflammatory bowel disease
+ Indication                                              
+  Bloody stool
+  Abnormal pain
+ Colon preparation agent                                 
+  PEG-ELS 類
+ Cleansing time:                                         
+  Morning single dose                                    
+ Cleansing Level:                                        
+  Good                                                   
+ Instrument:                                             
+  CF-Q260AI                  .17               
+ Insertion level:                                        
+  Cecum                                                  
+ Pre-mediction:                                          
+  Hyoscine butylbromide                                  
+ Sedation                                                
+  Propofol
+  Fentanyl(含Alfentanyl)
+ Accessibility:                                          
+  Easy                                                   
+ Anti-platelet/Anti-coagulant agents                     
+  Nil
+ Colonoscopic Findings                                   
+  The scope was inserted into cecum. There was a 0.5cm 0-Is adenoma, located 
+  within cecum, close to appendiceal orifice, polypectomy with cold snare 
+  excision was done(A). There was a 2.5cm 0-Isp lateral spreading tumor, with 
+  chicken skin change of surround mucosal, identified at upper rectum, 15cm AAV. 
+  The lesion could be elevated after submucosal saline injection, so EMR was 
+  performed, followed with metalic clips x 5 for closure of mucosal defect. 
+  However, due to malignancy still could not be complete ruled out, and 
+  considering about further follow up or possible surgical treatment, ink 
+  injection was also performed as tottoo localization. Mixed hemorrhoids were 
+  also noted.
+ Diagnosis                                                                       檢體總數:                     2           
+  Tubular adenoma,O-ls,Cecum,0.5cm,(A),S/p cold snare polypectomy
+  Villous adenoma,LST-NG(Laterally spreading tumor,non-granular 
+  type),Rectum,2.0cm,S/p tattooing,S/p EMR (Endoscopic mucosal resection),S/p 
+  hemoclipping,(B)
+  Mixed hemorrhoids
+ Complication                                            
+  Nil
+ Suggestion                                              
+  f/u</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+1. Large intestine, labeled "(A) ecum", colonoscopic polypectomy: tubular adenoma
+2. Large intestine, labeled "(B) rectum", endoscopic mucosal resection: tubulovillous adenoma with focal high-grade dysplasia
+GROSS:
+Specimens labeled as the following are received:
+1. "(A) ecum": one piece of tan to brown and elastic tissue fragment fixed in formalin and measuring 0.4 x 0.3 x 0.2 cm. (block A, totally submitted)
+2. "(B) rectum": two pieces of brown and elastic tissue fragments fixed in formalin and measuring 1.4 x 1.2 x 0.9 and 1.5 x 1.4 x 1.0 cm. (block B, totally submitted)
+The specimens are submitted as above. 
+MICROSCOPIC FINDINGS:
+Section A:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Section B:
+a. Histological diagnosis: tubulovillous adenoma with focal high-grade dysplasia
+b. Histological grade: high-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status: free from involvement (4 mm in distance)
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ecum, S/p cold snare polypectomy, 0.5cm.
+B: Tubulovillous adenoma, Rectum, S/p EMR, 2.0cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 1)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: Yes
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690002866</t>
+  </si>
+  <si>
+    <t>病歷號:OOOOOOO
+ 姓  名:OOO            大腸鏡檢查過程記錄暨報告
+ 生  日:西元 OOOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
+   檢查日期:  20200311            性別: M               流水序號:  報告流水號
+          Start time: 14  時 31 分 38 秒
+     Reach cecum at : 14  時 47 分 42 秒
+          End  time:  15  時 18 分 40 秒
+ Clinical Diagnosis :
+   positive iFOBT
+ Indication :
+   國民健康署糞便潛血檢查陽性
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Morning single dose
+ Cleansing Level :
+   Fair
+ Instrument :
+   CF          
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   None
+ Accessibility :
+   fair
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   Up to cecum, some fecal material was noted in the colon
+   One 0.2cm 0-IIa polyp was noted over cecum s/p biopsy removal(A)
+   One 0.2cm 0-IIa polyp was noted over A-colon s/p biopsy removal(B) with mild 
+   bleeding s/p hemoclipping x I
+   One 0.4cm 0-IIa polyp was noted over hepatic flexure s/p polypectomy with 
+   mild bleeding s/p hemoclipping
+   One 0.3cm 0-IIa polyp was noted over T-colon s/p biopsy removal(C) 
+   One 0.4cm 0-IIa polyp was noted over T-colon s/p biopsy removal(D) with mild 
+   bleeding s/p hemoclipping x I
+   One 1.5cm LST-NG was noted over splenic flexure
+   One 0.6cm 0-Is polyp was noted over proximal D-colon
+   One 0.9cm 0-Is polyp was noted over S-colon s/p polypectomy(E) followed by 
+   hemoclipping x II
+   One 0.4cm 0-IIa polyp was noted over rectum s/p biopsy removal(F) with mild 
+   bleeding s/p hemoclipping
+   Internal hemorrhoid was noted.
+ Endoscopic diagnosis :
+   Tubular adenoma,IIa,Cecum,0.2cm,S/p biopsy,(A)
+   Tubular adenoma,IIa,Ascending colon,0.2cm,S/p biopsy,S/p hemoclipping,(B)
+   Tubular adenoma,IIa,Transverse colon,0.3cm,S/p biopsy,(C)
+   Tubular adenoma,IIa,Transverse colon,0.4cm,S/p biopsy,S/p hemoclipping,(D)
+   Tubular adenoma,Is,Sigmoid colon,0.9cm,S/p polypectomy,S/p hemoclipping,(E)
+   Tubular adenoma,IIa,Rectum,0.4cm,S/p biopsy,S/p hemoclipping,(F)
+   Tubular adenoma,IIa,hepatic flexure,s/p polypectomy,s/p hemoclipping
+   Tubular adenoma,LST-NG, splenicflexure, 1.5cm,Splenic flexure
+   Tubular adenoma, Is, proximal D-colon
+   Internal hemorrhoid
+ Complication :
+   NIL
+ Suggestion :
+   post-EMR care and pursue the pathology result
+   Polypectomy of splenic flexure polyp was not performed this time due to 
+   bleeding tendency
+   Consider IVG examination next time
+   助理:   
+ 檢查者:                          /                       /OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Cecal polyp, labeled as A, biopsy removal: tubular adenoma 
+Ascending colon polyp, labeled as B, biopsy removal: tubular adenoma 
+Transverse colon polyp, labeled as C, biopsy removal: tubular adenoma 
+Transverse colon polyp, labeled as D, biopsy removal: tubular adenoma 
+Sigmoid colon polyp, labeled as E, polypectomy: tubular adenoma with free margin
+Rectal polyp, labeled as F, biopsy removal: hyperplastic polyp
+Colon Neoplastic polyp checklists
+2013/07/19病理部品管會議通過第一版
+MACROSCOPIC :
+1.	Lesion site : 
+A: Cecum 
+B: Ascending colon
+C and D: Transverse colon
+E: Sigmoid
+F: Rectum
+2.	Specimen type : 
+A, B, C, D and F: Biopsy
+E: Polypectomy 
+3.	Quantity: 
+The specimen A submitted consists of 1 tissue fragment measuring 0.2 cm in formalin. Total tissue is submitted in cassette A.
+The specimen B submitted consists of 1 tissue fragment measuring 0.2 cm fixed in formalin. Total tissue is submitted in cassette B.
+The specimen C submitted consists of 1 tissue fragment measuring 0.4 cm fixed in formalin. Total tissue is submitted in cassette C.
+The specimen D submitted consists of 1 tissue fragment measuring 0.4 cm in formalin. Total tissue is submitted in cassette D.
+The specimen E submitted consists of 2 tissue fragments measuring 0.2-0.7 cm fixed in formalin. Total tissue is submitted in cassette E.
+The specimen F submitted consists of 1 tissue fragment measuring 0.3 cm fixed in formalin. Total tissue is submitted in cassette F. 
+MICROSCOPIC:
+1.	Histological diagnosis:
+Neoplastic polyp
+I.	Adenoma: 
+A to E: Tubular adenoma 
+2.	Histological grade:
+A to E: Low grade dysplasia (including mild and moderate dysplasia)
+3.	*Margins status ( including stalk):
+E: Margin(s) uninvolved by tumor.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Cecum, S/p biopsy, 0.2cm.
+B: Tubular adenoma, Ascending colon, S/p biopsy and S/p hemoclipping, 0.2cm.
+C: Tubular adenoma, Transverse colon, S/p biopsy, 0.3cm.
+D: Tubular adenoma, Transverse colon, S/p biopsy and S/p hemoclipping, 0.4cm.
+E: Tubular adenoma, Sigmoid colon, S/p polypectomy and S/p hemoclipping, 0.9cm.
+F: Hyperplastic polyp, Rectum, S/p biopsy, 0.4cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 5 (less than 10mm: 5, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690002997</t>
+  </si>
+  <si>
+    <t>Clinical Diagnosis                                      
+  R/O colonic lesion
+ Indication                                              
+  國民健康署糞便潛血檢查陽性
+ Colon preparation agent                                 
+  PEG-ELS 類
+ Cleansing time:                                         
+  Evening single dose                                    
+ Cleansing Level:                                        
+  Fair                                                   
+ Instrument:                                             
+  CF-Q260AI                  .14               
+ Insertion level:                                        
+  Cecum                                                  
+ Pre-mediction:                                          
+  Hyoscine butylbromide                                  
+ Sedation                                                
+  None
+ Accessibility:                                          
+  Difficult                                              
+ Anti-platelet/Anti-coagulant agents                     
+  None
+ Colonoscopic Findings                                   
+  Up to cecum, some fecal material was noted. One 0.5cm 0-IIa polyp was noted 
+  at A-colon s/p biopsy with removal(A). One 0.2cm out-pouching lesion was noted 
+  at A-colon. One 1.5cm 0-IIa polyp was noted at D-colon s/p EMR; then oozing 
+  ensued and hemoclips x4 was appiled for wound closure(B). External hemorrhoid 
+  was noted. 
+ Diagnosis                                                                       檢體總數:                     2           
+  Tubular adenoma,lla,Ascending colon,0.5cm,S/p blopsy and removal,(A)
+  Tubular adenoma,LST-NG,Descending colon,1.5cm,S/p EMR,(B)
+  External hemorrhoids
+  Diverticulum, A-colon.
+ Complication                                            
+  Nil
+ Suggestion                                              
+  Post EMR care and pursue pathology report</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+1. Large intestine, labeled "(A) A-colon", colonoscopic biopsy: hyperplastic polyp
+2. Large intestine, labeled "(B) D-colon", colonoscopic mucosal resection: tubular adenoma
+GROSS:
+Two bottles labeled as following are received:
+1. "(A) A-colon": three pieces of tan and soft to elastic tissue fragments measuring 0.2 x 0.1 x 0.1 to 0.3 x 0.2 x 0.1 cm. (block A, totally submitted)
+2. "(B) D-colon": one piece of brown and elastic tissue fragment measuring 0.8 x 0.5 x 0.5 cm. (block B, totally submitted)
+The specimens are submitted as above. 
+MICROSCOPIC FINDINGS:
+Section A:
+a. Histological diagnosis: hyperplastic polyp
+b. Histological grade: not applicable
+c. Margin status (for high grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Section B:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Hyperplastic polyp, A-colon, S/p biopsy, 0.5cm.
+B: Tubular adenoma, D-colon, S/p EMR, 1.5cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690003576</t>
+  </si>
+  <si>
+    <t>病歷號:OOOOOOO
+ 姓  名:OOO            大腸鏡檢查過程記錄暨報告
+ 生  日:西元 OOOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
+   檢查日期:  20201105            性別: F               流水序號:  報告流水號
+          Start time: 15  時 11 分 32 秒
+     Reach cecum at : 15  時 17 分 22 秒
+          End  time:  15  時 52 分 34 秒
+ Clinical Diagnosis :
+   positive iFOBT
+ Indication :
+   國民健康署糞便潛血檢查陽性
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Morning single dose
+ Cleansing Level :
+   Poor
+ Instrument :
+   CF            
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   fair
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   Up to cecum, much fecal material was noted in the colon
+   One 0.3cm 0-IIa polyp was noted over A-colon s/p biopsy removal(A)
+   Out-punching lesions were noted over hepatic flexure.
+   One 1.6cm LST-NG was noted over hepatic flexure s/p EMR(D) after glycerol 
+   injection followed by hemoclipping x III
+   One 0.3cm 0-IIa polyp was noted over T-colon s/p biopsy removal(B)
+   One 0.4cm 0-IIa polyp was noted over T-colon s/p biopsy removal(C)
+   Internal hemorrhoid was noted.
+ Endoscopic diagnosis :
+   Tubular adenoma,IIa,Ascending colon,0.3cm,S/p biopsy and removal,(A)
+   Tubular adenoma,IIa,Transverse colon,0.3cm,S/p biopsy and removal,(B)
+   Tubular adenoma,IIa,Transverse colon,0.4cm,S/p biopsy and removal,(C)
+   Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular type),Hepatic 
+   flexure,1.6cm,S/p EMR (Endoscopic mucosal resection),S/p hemoclipping,(D)
+   Colonic diverticulosis,Ascending colon
+   Internal hemorrhoid
+ Complication :
+   NIL
+ Suggestion :
+   post-EMR care and pursue the pathlogy result
+   助理:   
+ 檢查者:                          /                       /OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Intestine, large, ascending colon, colonoscopic biopsy, tubular adenoma.
+Intestine, large, transverse colon, colonoscopic biopsy, tubular adenoma.
+Intestine, large, transverse colon, colonoscopic biopsy, tubular adenoma.
+Intestine, large, hepatic flexure, colonoscopic EMR, sessile serrated adenoma.
+Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
+MACROSCOPIC:
+1. Lesion site: 
+    A: Ascending colon    B: transverse colon
+    C: transverse colon      D: hepatic flexure
+2. Specimen type: 
+    A: Biopsy    B: Biopsy    C: Biopsy   D: EMR
+3. Quantity: 
+    A: Two tissue fragments, up to 0.3x0.2x0.15 cm in size
+    B: Two tissue fragments, up to 0.25x0.15x0.15cm in size
+    C: Two tissue fragments, up to 0.25x0.2x0.151 cm in size
+    D: One tissue fragment, 1x0.8x0.2 cm in size
+4. Comment: Nil 
+All for section and labeled as:                  Jar 0
+    A: Ascending colon    B: transverse colon
+    C: transverse colon      D: hepatic flexure
+MICROSCOPIC:
+1. Histological diagnosis:
+Neoplastic polyp
+I. Adenoma: 
+Tubular adenoma 
+II. Serrated adenoma/polyp: 
+Sessile serrated adenoma/polyp  
+2. Histological grade:
+Low grade dysplasia (including mild and moderate dysplasia)
+3. Margins status (including stalk):
+Margin(s) cannot be assessed : sections A, B, C
+Margin(s) uninvolved : section D
+4. Comment: Nil</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ascending colon, S/p biopsy and removal, 0.3cm.
+B: Tubular adenoma, Transverse colon, S/p biopsy and removal, 0.3cm.
+C: Tubular adenoma, Transverse colon, S/p biopsy and removal, 0.4cm.
+D: Sessile serrated adenoma/polyp, Hepatic flexure, S/p EMR and hemoclipping, 1.6cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 3 (less than 10mm: 3, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690005994</t>
+  </si>
+  <si>
+    <t>Clinical Diagnosis                                      
+  Positive iFOBT
+ Indication                                              
+  國民健康署糞便潛血檢查陽性
+ Colon preparation agent                                 
+  PEG-ELS 類
+ Cleansing time:                                         
+  Morning single dose                                    
+ Cleansing Level:                                        
+  Good                                                   
+ Instrument:                                             
+  CF-Q260AI                  .23               
+ Insertion level:                                        
+  Cecum                                                  
+ Pre-mediction:                                          
+  Hyoscine butylbromide                                  
+ Sedation                                                
+  Midazolam(Dormicum)
+  Propofol
+  Fentanyl(含Alfentanyl)
+ Accessibility:                                          
+  Easy                                                   
+ Anti-platelet/Anti-coagulant agents                     
+  Nil
+ Colonoscopic Findings                                   
+  A 0.6cm 0-IIa polyp at A-colon s/p cold-snaring polypectomy 
+  (A). A 1.5cm LST-NG at rectum s/p EMR followed by 
+  hemoclipping*2(B).
+ Diagnosis                                                                       檢體總數:                     2           
+  Sessile serrated adenoma,O-lla,Ascending colon,0.6cm,(A),S/p 
+  cold snare polypectomy
+  Tubulovillous adenoma,LST-NG(Laterally spreading tumor,non-
+  granular type),Rectum,S/p EMR (Endoscopic mucosal 
+  resection),S/p hemoclipping,(B)
+ Complication                                            
+  Nil
+ Suggestion                                              
+  Post EMR care and pursue pathology report</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+1. Large intestine, labeled "(A) A-colon", colonoscopic polypectomy: hyperplastic polyp
+2. Large intestine, labeled "(B) rectum", colonoscopic mucosal resection: tubular adenoma
+GROSS:
+Two bottles labeled as following are received:
+1. "(A) A-colon": three pieces of tan and elastic tissue fragments measuring 0.5 x 0.1 x 0.1 cm. (block A, totally submitted)
+2. "(B) rectum": one piece of tan and elastic tissue fragment measuring 1.2 x 0.7 x 0.7 cm. (block B, totally submitted)
+The specimens are submitted as above.
+MICROSCOPIC FINDINGS:
+Section A:
+a. Histological diagnosis: hyperplastic polyp
+b. Presence of high grade dysplasia: not applicable
+c. Margin status (for high grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Section B:
+a. Histological diagnosis: tubular adenoma
+b. Presence of high grade dysplasia: absent
+c. Margin status (for high grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Hyperplastic polyp, A-colon, S/p colonoscopic polypectomy, 0.6cm.
+B: Tubular adenoma, Rectum, S/p EMR and hemoclipping, 1.5cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690006016</t>
+  </si>
+  <si>
+    <t>病歷號: OOOOOOO
+ 姓  名:OOO             大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOO         年齡: 47              保險身分:   
+   檢查日期:  20240905            性別: F               流水序號:  報告流水號
+          Start time:    11 時  30 分 35 秒
+     Reach cecum at :    11 時  34 分 20 秒
+          End  time:     11 時  48 分 19 秒
+ Clinical Diagnosis :
+   Health exam
+ Indication :
+   Health exam
+ Colon preparation agent :
+   Magnesium citrate類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Good
+ Instrument :
+   EC-760R                       
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Easy
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   The scope was inserted to the cecum. One 0.4 cm IIa NICE type 2 lesion was 
+   noted at the A-colon S/p CSP (A). One 1.0 cm LST-NG NICE type 2 lesion was 
+   noted at the D-colon S/p CSP (B). Mixed hemorrhoids were noted.
+ Endoscopic diagnosis :
+   Tubular adenoma,IIa,Ascending colon,0.4cm,S/p cold snare polypectomy,(A)
+   Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular 
+   type),Descending colon,1cm,S/p cold snare polypectomy,(B)
+   Mixed hemorrhoids
+ Complication :
+   NIL
+ Suggestion :
+     技術員: OOO     檢查者:                         / OOO主治醫師</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+Intestine, large, ascending, labeled A, colonoscopic polypectomy --- tubular adenoma
+Intestine, large, descending, labeled B, colonoscopic polypectomy --- tubular adenoma
+GROSS FINDINGS:
+The specimen A submitted consists of a tissue fragment measuring 0.7 x 0.5 x 0.2 cm in size, fixed in formalin.
+Grossly, it is tan to tannish brown and elastic. 
+All for section and labeled as A.
+The specimen B submitted consists of 3 tissue fragments measuring up to 2.0 x 0.5 x 0.4 cm in size, fixed in formalin.
+Grossly, they are tan to tannish brown and elastic. 
+All for section and labeled as B.
+MICROSCOPIC FINDINGS:
+Specimen A:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen B:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low-grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.4cm, Low-grade dysplasia (including mild and moderate dysplasia), Uninvolved margins.
+B: Tubular adenoma, Descending colon, S/p cold snare polypectomy, 1cm, Low-grade dysplasia (including mild and moderate dysplasia), Uninvolved margins.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690006051</t>
+  </si>
+  <si>
+    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
+病歷號:OOOOOOOO             National Taiwan University  Hospital
+姓　名: OOO
+                          大腸鏡檢查過程紀錄暨報告
+生　日: OOOOOOOO                                                             第 1  頁
+   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
+   檢查日期:  20210930            性別: M               流水序號:  報告流水號
+ Examination time :Start time :                   End time :   
+ Clinical Diagnosis :
+   colon polyps
+ Indication :
+   Post polypectomy surveillance
+ Colon preparation :
+   Niflec
+ Condition :
+   Fair
+ Instrument :
+   CF-H290L  2041499
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Buscopan
+ Anesthesia :
+   Dromucum+Rapifen+Propofol
+ Cleansing time :
+   Morning
+ Medication history :
+   Nil
+ Colonoscopic Findings :
+   Up to cecum, some fecal material was noted in the colon.
+   Redundant S-colon was noted.
+   One 1.6cm LST-NG was noted over A-colon s/p EMR(A) after glycerol injection 
+   followed by hemoclipping x IV
+   One 0.3cm 0-IIa polyp was noted over A-colon s/p biopsy removal(B)
+   ONe 0.5cm 0-Is polyp was noted over D-colon s/p polypectomy(C) followed by 
+   hemoclipping x II
+   One 0.2cm 0-IIa polyp was noted over rectum s/p biopsy removal(D)
+   One 1.3cm 0-Is polyp was noted over rectum s/p EMR(E) after glycerol 
+   injection followed by hemoclipping x III
+   Internal hemorrhoid was noted.
+ Endoscopic Diagnosis :
+   Probably tubular adenoma, LST-NG, A-colon, s/p EMR(A) and hemoclipping
+   Probably tubular adenoma, 0-IIa, A-colon, s/p biopsy removal(B)
+   Probably tubular adenoma, 0-Is, D-colon, s/p polypectomy(C) and hemoclipping
+   Probably tubular adenoma, 0-Is, rectum, s/p biopsy removal(D)
+   Probably tubular adenoma, 0-Is, rectum, s/p EMR(E) and hemoclipping
+   Internal hemorrhoid.
+ Complication :
+   Negative
+ Suggestion :
+   Post EMR care and pursue pathology report
+ Specimens :
+   5 bottles
+   助理:   
+ 檢查者:                          /                        / OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Intestine, large, ascending colon (A), colonoscopic EMR, tubular adenoma.
+Intestine, large, ascending colon (B), colonoscopic biopsy, tubular adenoma.
+Intestine, large, descending colon, colonoscopic polypectomy, tubular adenoma.
+Intestine, large, rectum (D), colonoscopic biopsy, hyperplastic polyp.
+Intestine, large, rectum (E), colonoscopic EMR, tubulovillous adenoma.
+Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
+MACROSCOPIC:
+1. Lesion site: 
+    A: ascending colon    B: ascending colon 
+    C: descending colon    D: rectum     E: rectum
+2. Specimen type: 
+    A: EMR    B: biopsy    C: polypectomy   D: biopsy   E: EMR
+3. Quantity: 
+    A: One tissue fragment, 0.95x0.7x0.6 cm in size
+    B: One tissue fragment, 0.3x0.2x0.2 cm in size
+    C: One tissue fragment, 0.45x0.4x0.35 cm in size
+    D: One tissue fragment, 0.25x0.2x0.15 cm in size
+    E: One tissue fragment, 1x1x0.95 cm in size 
+4. Comment: Nil 
+All for section and labeled as:                  Jar 0
+    A1: ascending colon    B1: ascending colon 
+    C1: descending colon    D1: rectum     E1: rectum
+MICROSCOPIC:
+1. Histological diagnosis:
+Neoplastic polyp
+I. Adenoma: 
+Tubular adenoma 
+Tubulovillous adenoma  
+2. Histological grade:
+Low grade dysplasia (including mild and moderate dysplasia)
+3. Margins status (including stalk):
+Margin(s) uninvolved 
+4. Comment: Nil</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ascending colon, S/p EMR and hemoclipping, 1.6cm.
+B: Tubular adenoma, Ascending colon, S/p biopsy removal, 0.3cm.
+C: Tubular adenoma, Descending colon, S/p polypectomy and hemoclipping, 0.5cm.
+D: Hyperplastic polyp, Rectum, S/p biopsy removal, 0.2cm.
+E: Tubulovillous adenoma, Rectum, S/p EMR and hemoclipping, 1.3cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 4 (less than 10mm: 2, 10-19mm: 2, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: Yes
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690008210</t>
+  </si>
+  <si>
+    <t>國 立 台 灣 大 學 醫 學 院 附 設 醫 院
+ 病歷號:OOOOOOO            National Taiwan University Hospital 
+ 姓  名:OOO           大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOO           (綜診部內視鏡中心)                           第 1  頁
+   檢查單號:  OOOOOO         年齡: 82              保險身分:   
+   檢查日期:  OOOOOO            性別: F               流水序號:  OOOOOO
+          Start time:    15 時  22 分 46 秒
+     Reach cecum at :    15 時  26 分 51 秒
+          End  time:     15 時  47 分 28 秒
+ Clinical Diagnosis :
+   For post LAR follow-up
+ Indication :
+   大腸癌術後追蹤
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Good
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Instrument :
+   CF Q260AI.16
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Fair
+ Colonoscopic Findings :
+   The scope was inserted to the cecum smoothly. A 0.5 cm NICE type 2 polypoid 
+   lesion was noted over transverse colon. Cold snare polypectomy was performed
+   (A). Lateral spreading lesion, 1 cm, was noted over anastomotic site, on the 
+   stitch. Cold snare was used for biopsy(B). A 0.3 cm  NICE type 2 polypoid 
+   lesion was noted over anastomotic site. Cold snare polypectomy was 
+   performed but the specimen was lost.
+   Diverticulae were noted over ascending colon. Operation scar was noted, 
+   compatible with post LAR change.
+ Endoscopic diagnosis :
+   Tubular adenoma,IIa,Transverse colon,0.5cm,S/p cold snare polypectomy,(A)
+   Colon tumor， r/o recurrenct,Anastomosis,S/p biopsy,(B)
+   Tubular adenoma,IIa,Anastomosis,0.3cm,S/p cold snare polypectomy,(lost)
+   S/P partial colectomy
+ Specimens :
+   2    bottle(s)
+ Complication :
+   NIL
+ Suggestion :
+   General surgeon OPD follow-up
+   Post polypectomy care and pursue pathology report
+   Avoid heavy lifting for one week
+   watch out bleeding sign
+   助理:  OOO護理師
+ 檢查者:  OOO住院醫師           /                        / OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Intestine, large, colon, transverse, colonoscopic cold snare polypectomy, tubular adenoma
+Intestine, large, anastomosis  colonoscopic biopsy, inflamed granulation tissue
+MACROSCOPIC:
+A: 1 tissue fragment, 0.5 x 0.2 x 0.1 cm in size
+B: 1 tissue fragment, 0.4 x 0.3 x 0.1 cm in size
+All for sections and labeled as:    Jar 0
+A1: transverse colon
+B1: anastomosis 
+MICROSCOPIC:
+* Histological diagnosis:
+A: tubular adenoma
+B: inflamed granulation tissue with focal glandular epithelial hyeperplasia
+* High grade dysplasia (including severe dysplasia and carcinoma in situ): Absent
+* Surgical margin: 
+Section A: Uninvolved 
+Section B: Uninvolved 
+* Comment(s): CK-immunostain performed in section B1 shows no presence of immuno-positive atypical cells in inflamed tissue.
+Ref:
+總院 S2316038
+[01]. Intestine, large, rectum, total mesorectal excision, adenocarcinoma
+[02]. Intestine, large, proximal margin, resection, no evidence of malignancy
+[03]. Intestine, large, distal margin, resection, no evidence of malignancy
+[04]. Lymph node, regional, lymphadenectomy, carcinoma, metastatic, (positive/total: 3/19)</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Tubular adenoma, Transverse colon, S/p cold snare polypectomy, 0.5cm.
+B: Inflamed granulation tissue with focal glandular epithelial hyperplasia, Anastomosis, S/p biopsy, (no size mentioned).
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 1 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+7-10 Years</t>
+  </si>
+  <si>
+    <t>P250690008808</t>
+  </si>
+  <si>
+    <t>病歷號: OOOOOOO
+ 姓  名:OOO             大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOO         年齡: 46              保險身分:   
+   檢查日期:  20240906            性別: M               流水序號:  報告流水號
+          Start time:    15 時  33 分 46 秒
+     Reach cecum at :    15 時  36 分 12 秒
+          End  time:     16 時  31 分 30 秒
+ Clinical Diagnosis :
+   Colon polyp history
+ Indication :
+   瘜肉或腫瘤切除
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Morning single dose
+ Cleansing Level :
+   Poor
+ Instrument :
+   CF-HQ290I                    223
+ Insertion level :
+   Terminal ileum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Fair
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   The scope was inserted to the cecum smoothly. A 2.0cm lateral spreading 
+   tumor, homogeneous type was noted over transverse colon. Hot EMR was 
+   performed(A). Hemoclips was used for hemostasis. Another 1.5 cm lateral 
+   spreading tumor was noted over transverse colon. Hot EMR was performed(B). 
+   Hemoclips was used for hemostasis.
+ Endoscopic diagnosis :
+   Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular 
+   type),Transverse colon,2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemostasis,S/p hemoclipping,(A)
+   Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular 
+   type),Transverse colon,1.5cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemostasis,S/p hemoclipping,(B)
+ Complication :
+   NIL
+ Suggestion :
+   Post EMR care and pursue pathology report
+     技術員: OOO
+     檢查者: 黃詮博                  / OOO主治醫師(內專醫字第OOO號)</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+Intestine, large, transverse, labeled A, endoscopic mucosal resection --- hyperplastic polyp
+Intestine, large, transverse, labeled B, endoscopic mucosal resection --- sessile serrated lesion
+GROSS FINDINGS:
+The specimen A submitted consists of 2 tissue fragments measuring 0.7 x 0.5 x 0.4 cm and 0.5 x 0.3 x 0.2 cm in size, fixed in formalin.
+Grossly, they are tan and elastic. 
+All for section and labeled as A.
+The specimen B submitted consists of a tissue fragment measuring 1.1 x 0.5 x 0.3 cm in size, fixed in formalin.
+Grossly, it is tan and elastic. 
+All for section and labeled as B.
+MICROSCOPIC FINDINGS:
+Specimen A:
+a. Histological diagnosis: hyperplastic polyp
+b. Histological grade: not applicable
+c. Margin status (for high-grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+Specimen B:
+Sections show a picture of sessile serrated lesion, which is composed of irregular indentation of neoplastic epithelium containing slightly enlarged and hyperchromatic nuclei. The resection margin is involved.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Hyperplastic polyp, Transverse colon, S/p EMR, 2.0cm.
+B: Sessile serrated lesion, Transverse colon, S/p EMR, 1.5cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690011773</t>
+  </si>
+  <si>
+    <t>Starting time : 09時20分12秒
+   Reach time : 09時24分54秒
+   End time : 09時36分45秒
+Clinical Diagnosis : 
+      Suspect rectal lesion
+Indication : 
+      Suspect rectal lesion
+Colon preparation agent : 
+      PEG-ELS類
+Cleansing Time :       Morning single dose
+Cleansing Level :       Good
+Instrument :       PCF-H290Z 3 
+Insertion Level :       Cecum
+Pre-Medication :       Hyoscine butylbromide
+Sedation : 
+      IVGA
+Accessibility :       Easy
+Anti-platelet/Anti-coagulant agents : 
+      none
+Colonoscopic Findings : 
+      Faint erythematous area was noted at lower rectum without clear border. Although JNET type 2A vascular pattern was noted at some area, no obvious abnormal pit pattern was noted after chromoendoscopy by indigo carmine. Biopsy to these regions were done. Internal hemorrhoid.
+Endoscopic Diagnosis : 
+      Inflammatory polyp, LST-NG(Laterally spreading tumor,non-granular type) ; Rectum ; S/p biopsy and removal  ; (A)
+      Internal hemorrhoid
+Complication : 
+      Nil
+Suggestion : 
+      Nil
+助理檢查人員 :   OOO
+醫師科別 :    消化腸胃系內科</t>
+  </si>
+  <si>
+    <t>Intestine, large, rectum, colonoscopic biopsy, chronic active colitis
+MACROSCOPIC :
+Three tissue fragments, up to 0.2 x 0.2 x 0.2 cm in size 
+All for section and labeled as:    Jar 0
+MICROSCOPIC :
+   It shows mixed neutrophils and lymphoplasma cells infiltration in the lamina propria. Granulation tissue formation is also noted. By special stain, no definite pathogen is highlighted by PAS or GMS stains. No occult carcinoma is demonstrated by cytokeratin immunostain.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Inflammatory polyp, Rectum, S/p biopsy and removal, (no size mentioned).
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+10 Years</t>
+  </si>
+  <si>
+    <t>P250690009384</t>
+  </si>
+  <si>
+    <t>Starting time : 11時11分00秒
+   Reach time : 11時20分05秒
+   End time : 11時31分00秒
+Clinical Diagnosis : 
+      Abdominal pain.
+Indication : 
+      Abdominal pain.
+Colon preparation agent : 
+      PEG-ELS類
+Cleansing Time :       Evening single dose
+Cleansing Level :       Fair
+Instrument :       PCF-H290Z 4 
+Insertion Level :       Cecum
+Pre-Medication :       Hyoscine butylbromide
+Sedation : 
+      IVGA
+Accessibility :       Fair
+Anti-platelet/Anti-coagulant agents : 
+      Nil
+Colonoscopic Findings : 
+      The endoscope was inserted into the cecum. Some mud-like and solid stool fragments were found along the course. A 1.2cm NICE II LST-NG was noted at H/F and CSP was done with HSP applied for breaking the submucosal cord and the wound was closed with clipping x1 (A). Multiple outpouches were noted at the A/C and S/C. Engorged vasculatures were found above and below the dentate line.
+Endoscopic Diagnosis : 
+      Tubular adenoma, LST-NG(Laterally spreading tumor,non-granular type) ; Hepatic flexure ; 1.2 cm ; S/p hot snare polypectomy ; S/p cold snare polypectomy ; S/p hemoclipping ; (A)
+      Colonic diverticulosis ; Ascending colon ; Sigmoid colon ; 
+      Mixed hemorrhoids
+Complication : 
+      Nil
+Suggestion : 
+      Post polypectomy care and pursue pathology report.
+助理檢查人員 :   OOO
+醫師科別 :    消化腸胃系內科</t>
+  </si>
+  <si>
+    <t>Intestine, large, colon, hepatic flexure, endoscopic biopsy, tubular adenoma
+MACROSCOPIC :
+* Quantity: two tissue fragments, up to 1.2 x 0.4 x 0.2 cm in size
+All for section                                           Jar 0
+MICROSCOPIC :
+* Histological diagnosis: tubular adenoma
+* High grade dysplasia (including severe dysplasia and carcinoma in situ): Absent
+* Invasive carcinoma: Absent
+* Surgical margin: Cannot be assessed in biopsy specimen</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Hepatic flexure, S/p hot snare polypectomy, 1.2cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690010115</t>
+  </si>
+  <si>
+    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
+                                                   National Taiwan University Hospital  Hsin-Chu Hospital
+ 病歷號: OOOOOOO
+ 姓  名: OOO
+                                 大腸鏡檢查過程紀錄暨報告
+ 生  日: OOOOOOOO
+檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20230315
+          Start time:    14 時  26 分 35 秒
+     Reach cecum at :    14 時  31 分 27 秒
+          End  time:     14 時  49 分 42 秒
+ Clinical Diagnosis :
+   iFOBT positive
+ Indication :
+   國民健康署糞便潛血檢查陽性
+ Colon preparation agent :
+   Phosphosoda類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Good
+ Instrument :
+   CF-H290I                     223
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Hyoscine butylbromide
+ Sedation :
+   Midazolam (Dormicum)
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Easy
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   The scope was inserted into cecum. There was a 2.0cm IIa-IIc lateral 
+   spreading tumor, non-granular type, located at A-colon. Still could be lifted 
+   after submucosal saline injection. Hot EMR was then performed, followed with 
+   hemoclipping x 2 for closure of mucosal defect(A). Mixed hemorrhoids were 
+   also noted.
+ Endoscopic diagnosis :
+   Tubulovillous adenoma,LST-NG(Laterally spreading tumor,non-granular 
+   type),Ascending colon,2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(A)
+   Mixed hemorrhoids
+ Complication :
+   NIL
+ Suggestion :
+   post EMR care
+   OPD f/u
+ 檢查者:OOO       / 住院醫師:          OOO主治醫師:OOO主治醫師(台消外專科證字第OOOO號)</t>
+  </si>
+  <si>
+    <t>PATHOLOGICAL DIAGNOSIS:
+Colon, A-colon, endoscopic mucosal resection(EMR): tubular adenoma
+GROSS:
+The specimen consists of one tissue fragment, 1.5x1.2x0.7 cm in size. The entire specimen is submitted in one cassette.
+MICROSCOPIC FINDINGS:
+a. Histological diagnosis: tubular adenoma
+b. Histological grade: low grade dysplasia (including mild and moderate dysplasia)
+c. Margin status (for high grade dysplasia or carcinoma): not applicable
+d. Lymphovascular invasion: not applicable
+e. Perineural invasion: not applicable
+f. Comments: nil.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ascending colon, S/p hot EMR (Endoscopic mucosal resection), 2cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 1 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 1)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690010979</t>
+  </si>
+  <si>
+    <t>Clinical Diagnosis                                      
+  Positive iFOBT
+ Indication                                              
+  國民健康署糞便潛血檢查陽性
+ Colon preparation agent                                 
+  PEG-ELS 類
+ Cleansing time:                                         
+  Morning single dose                                    
+ Cleansing Level:                                        
+  Good                                                   
+ Instrument:                                             
+  CF-HQ290I                  .1                
+ Insertion level:                                        
+  Cecum                                                  
+ Pre-mediction:                                          
+  Hyoscine butylbromide                                  
+ Sedation                                                
+  Midazolam(Dormicum)
+  Propofol
+  Fentanyl(含Alfentanyl)
+ Accessibility:                                          
+  Easy                                                   
+ Anti-platelet/Anti-coagulant agents                     
+  Clopidogrel(Plavix)   Hold 5 days
+ Colonoscopic Findings                                   
+  A 1.0cm LST-NG at cecum s/p EMR followed by hemoclipping*2(A). A 0.8cm 0-Is 
+  polyp at A-colon s/p polypectomy(B). Another 0.2cm 0-Is polyp at at A-colon 
+  s/p polypectomy(B). Another 0.8cm 0-Ip polyp at hepatic flexure s/p 
+  polypectomy(C). Several polyps were found over T-colon and S-colon.
+ Diagnosis                                                                       檢體總數:                     3           
+  Tubulovillous adenoma,LST-NG(Laterally spreading tumor,non-granular 
+  type),Cecum,1.0cm,S/p EMR (Endoscopic mucosal resection),S/p hemoclipping,(A)
+  Tubular adenoma,O-ls,Ascending colon,0.8cm,(B),S/p hot snare polypectomy
+  Tubular adenoma,O-ls,Ascending colon,0.2cm,(B),S/p cold snare polypectomy
+  Tubulovillous adenoma,O-lp,Hepatic flexure,0.8cm,(C),S/p hot snare polypectomy
+  Colon polyps, T-colon and S-colon
+ Complication                                            
+  Nil
+ Suggestion                                              
+  Post EMR care and pursue pathology report
+  Arrange CFS 3M later for further polypectomy for residual polyps
+  Hold plavix for 3 days</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS
+Large intestine, cecum (A), polypectomy 
+   ----Tubulovillous adenoma
+Large intestine, A-colon (B), polypectomy 
+   ----Tubular adenoma
+   ----Tubulovillous adenoma
+Large intestine, hepatic flexure (C), polypectomy 
+   ----Tubular adenoma
+GROSS DESCRIPTION
+   The specimen submitted consists of 3 bottles.   
+   Bottle A contains a tissue fragment measuring 1.3 x 0.8 x 0.5 cm.
+   Bottle B contains 5 tissue fragments measuring up to 0.9 x 0.8 x 0.5 cm.
+   Bottle C contains a tissue fragment measuring 0.8 x 0.7 x 0.5 cm.
+   All submitted (B as B1-2).
+MICROSCOPIC DESCRIPTION
+   Sections of specimen A show polypoid colonic mucosa with adenomatous and villous glands.
+   Sections of specimen B show polypoid colonic mucosae with adenomatous glands or adenomatous and villous glands.
+   Sections of specimen C both show polypoid colonic mucosa with adenomatous glands.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubulovillous adenoma, Cecum, S/p EMR and hemoclipping, 1.0cm.
+B: Tubular adenoma, Ascending colon, S/p hot snare polypectomy, 0.8cm.
+B: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.2cm.
+C: Tubular adenoma, Hepatic flexure, S/p hot snare polypectomy, 0.8cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 4 (less than 10mm: 3, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: Yes
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690011814</t>
+  </si>
+  <si>
+    <t>國立臺灣大學醫學院附設醫院新竹臺大分院新竹醫院
+                                                   National Taiwan University Hospital  Hsin-Chu Hospital
+ 病歷號: OOOOOOO
+ 姓  名: OOO
+                                 大腸鏡檢查過程紀錄暨報告
+ 生  日: OOOOOOOO
+檢查單號: OOOOOOOOO        年齡:OO          性別: M         檢查日期: 20230511
+          Start time:    14 時  44 分 13 秒
+     Reach cecum at :    14 時  46 分 43 秒
+          End  time:     15 時  14 分 14 秒
+ Clinical Diagnosis :
+   Colon polyp 
+ Indication :
+   國民健康署糞便潛血檢查陽性
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Poor
+ Instrument :
+   CF-H290I                     8
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Buscopan
+ Sedation :
+   Nil
+ Accessibility :
+   Easy
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   The scope was inserted to cecum. One 0.8cm 0-Is polyp was noted at A-colon, 
+   s/p cold snare polypectomy(A). One 1.2cm LST-NG was noted at A-colon, s/p 
+   endoscopic mucosal resection, s/p hemoclipping x 2(B). One 1.2cm LST-NG was 
+   noted at S-colon, s/p endoscopic mucosal resection, s/p hemoclipping x 2(C) 
+   MIxed hemorrhoid was seen.
+ Endoscopic diagnosis :
+   Tubular adenoma,Is,Ascending colon,0.8cm,S/p cold snare polypectomy,(A)
+   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
+   type),Ascending colon,1.2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(B)
+   Sessile serrated lesion(SSL),LST-NG(Laterally spreading tumor,non-granular 
+   type),Sigmoid colon,1.2cm,S/p hot EMR (Endoscopic muscosal resection),S/p 
+   hemoclipping,(C)
+   Mixed hemorrhoids
+   Poor preparation
+ Complication :
+   NIL
+ Suggestion :
+   Pursue pathology report
+ 技術員:OOO
+ 檢查者:OOO          / 住院醫師:          OOO主治醫師:OOO主治醫師(消專醫字第OOO號)</t>
+  </si>
+  <si>
+    <t>Intestine, large, colon, endoscopic polypectomy, 
+A: ascending, one, tubular adenoma
+B: ascending, two, sessile serrated lesion
+C: sigmoid, sessile serrated lesion
+[Gross description]
+1. Specimen size:
+   A: one, 0.5 x 0.4 x 0.3 cm 
+   B: one, 1.1 x 1.0 x 0.7 cm 
+   C: one, 1.2 x 0.9 x 0.5 cm 
+2. Tissue origin: 
+   A, B: A colon
+   C: S colon
+3. Gross description: tan and elastic
+  All for sections and labeled as: Jar 0
+  A-C
+[Microscopic description]
+1. Histological diagnosis: 
+   A: tubular adenoma
+   B: sessile serrated lesion
+   C: sessile serrated lesion 
+2. High-grade dysplasia or invasive carcinoma: absent
+3. Margin:  
+   A: cannot be assessed
+   B, C: uninvolved
+Ref: nil</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ascending colon, S/p cold snare polypectomy, 0.8cm.
+B: Sessile serrated lesion, Ascending colon, S/p hot EMR, S/p hemoclipping, 1.2cm.
+C: Sessile serrated lesion, Sigmoid colon, S/p hot EMR, S/p hemoclipping, 1.2cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 1 (less than 10mm: 1, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 2 (less than 10mm: 0, greater than or equal to 10mm: 2)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690010766</t>
+  </si>
+  <si>
+    <t>病歷號: OOOOOOO
+ 姓  名:OOO             大腸鏡檢查過程紀錄暨報告
+ 生  日:西元 OOOOOOO
+                                                                             第 1  頁
+   檢查單號:  OOOOOOOO         年齡: 79              保險身分:   
+   檢查日期:  20210106            性別: M               流水序號:  報告流水號
+          Start time:    14 時  28 分 08 秒
+     Reach cecum at :    14 時  31 分 35 秒
+          End  time:     14 時  44 分 53 秒
+ Clinical Diagnosis :
+   colon polyp
+ Indication :
+   瘜肉切除後追蹤
+ Colon preparation agent :
+   PEG-ELS類
+ Cleansing time :
+   Split dose
+ Cleansing Level :
+   Poor
+ Instrument :
+   CF-H290I                     .3
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Buscopan
+ Sedation :
+   Propofol
+   Fentanyl (含Alfentanyl)
+ Accessibility :
+   Easy
+ Anti-platelet / Anti-coagulant agents :
+   NIL
+ Colonoscopic Findings :
+   The scope was inserted to cecum. Much semifluid fecal material was noted. One 
+   1.2cm lateral spreading tumor was noted at A-colon, s/p endoscopic mucosal 
+   resection, s/p hemoclipping x 2. One 0.5cm 0-IIa polyp was noted at A-colon, 
+   s/p cold snare polypectomy(B). Mixed hrmorrhoid was seen.
+ Endoscopic diagnosis :
+   Tubular adenoma,LST-G(Laterally spreading tumor,granular type),Ascending 
+   colon,1.2cm,S/p EMR (Endoscopic mucosal resection),S/p hemoclipping,(A)
+   Tubular adenoma,IIa,Ascending colon,0.5cm,S/p cold snare polypectomy,(B)
+   Mixed hemorrhoids
+ Complication :
+   NIL
+ Suggestion :
+   Post EMR care and pursue pathology report
+     技術員: OOO
+     檢查者:                         / OOO主治醫師(台消內鏡專科證字第OOOOOO號)</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS:
+Intestine, large, A-colon, colonoscopic mucosal resection, --- sessile serrated adenoma
+Intestine, large, A-colon, colonoscopic polypectomy, --- hyperplastic polyp
+GROSS FINDINGS:
+1. Bottle A: One tissue fragment, 0.9 x 0.5 x 0.4 cm in size.
+2. Bottle B: One tissue fragment, 0.7 x 0.4 x 0.1 cm in size.
+All for sections and labeled as:
+  A: colon, EMR
+  B: colon, polypectomy
+MICROSCOPIC FINDINGS:
+1. Bottle A:
+a. Histological diagnosis: Sessile serrated adenoma
+b. Histological grade: Not applicable
+c. Margin status: Not applicable
+d. Lymphovascular invasion: Not applicable
+e. Perineural invasion: Not applicable
+2. Bottle B:
+a. Histological diagnosis: Hyperplastic polyp
+b. Histological grade: Not applicable
+c. Margin status: Not applicable
+d. Lymphovascular invasion: Not applicable
+e. Perineural invasion: Not applicable</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Sessile serrated adenoma, Ascending colon, S/p EMR, 1.2cm.
+B: Hyperplastic polyp, Ascending colon, S/p cold snare polypectomy, 0.5cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 0 (less than 10mm: 0, 10-19mm: 0, greater than or equal to 20mm: 0)
+Total SSPs: 1 (less than 10mm: 0, greater than or equal to 10mm: 1)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>P250690009156</t>
+  </si>
+  <si>
+    <t>國 立 臺 灣 大 學 醫 學 院 附 設 醫 院
+病歷號:OOOOOOOO             National Taiwan University  Hospital
+姓　名: OOO
+                          大腸鏡檢查過程紀錄暨報告
+生　日: OOOOOOOO                                                             第 1  頁
+   檢查單號:  OOOOOOOOOOO         年齡: OO              保險身分:   
+   檢查日期:  20250313            性別: M               流水序號:  報告流水號
+ Examination time :Start time :                   End time :   
+ Clinical Diagnosis :
+   Susp. colonic lesion
+ Indication :
+   Colon polyp noted outside
+ Colon preparation :
+   Niflec
+ Condition :
+   Good
+ Instrument :
+   CF-H290L  C2041499
+ Insertion level :
+   Cecum
+ Pre-medication :
+   Buscopan
+ Anesthesia :
+   Nil
+ Cleansing time :
+   Morning
+ Medication history :
+   Nil
+ Colonoscopic Findings :
+   Up to cecum, some fecal material was noted inside the colon. Three 
+   0.2-0.3cm 0-Is polyps were found at ascending colon and biopsy 
+   removal was done(A). Two 0.2-0.4cm 0-Is polyps were found at 
+   transverse colon and biopsy removal was done(B). Two 0.2-0.3cm 0-Is 
+   polyps were found at descending colon and biopsy removal was done(C). 
+   One 1.0cm nongranular laterally spreading tumor was found at sigmoid 
+   colon, 30cm above anal verge, and cold snaring polypectomy with 
+   hemoclipping(x2) was done(D). One 0.5cm 0-Is polyp was found at 
+   sigmoid colon during insertion and cold snaring polypectomy was done(E). 
+   Internal hemorrhoid was found. 
+ Endoscopic Diagnosis :
+   1.A-colon polyps(x3), suspected tubular adenomas, status post biopsy removal
+   (A)
+   2.T-colon polyps(x2), suspected tubular adenomas, status post biopsy removal
+   (B)
+   3.D-colon polyps(x2), suspected tubular adenomas, status post biopsy 
+   removal(C)
+   4.S-colon LST-NG, suspected tubular adenoma, status post cold snaring 
+   polypectomy(D)
+   5.S-colon polyp, suspected tubular adenoma, status post cold snaring 
+   polypectomy(E)
+   6.Internal hemorrhoid
+ Complication :
+   Negative
+ Suggestion :
+   Pursue the pathology report
+   Post-polypectomy care
+   Suggest regular CFS follow-up
+ Specimens :
+   5 bottles 
+   助理:   
+ 檢查者:                          /                        / OOO主治醫師</t>
+  </si>
+  <si>
+    <t>Intestine, large, ascending colon (A), colonoscopic biopsy, tubular adenoma.
+Intestine, large, transverse colon (B), colonoscopic biopsy, tubular adenoma.
+Intestine, large, descending colon (C), colonoscopic biopsy, tubular adenoma.
+Intestine, large, sigmoid colon (D), colonoscopic polypectomy, tubular adenoma.
+Intestine, large, sigmoid colon (E), colonoscopic polypectomy, tubular adenoma.
+Colon Neoplastic polyp checklists           2013/07/19病理部品管會議通過第一版
+MACROSCOPIC:
+1. Lesion site: 
+    A: ascending colon    B: transverse colon
+    C: descending colon   D: sigmoid colon     E: sigmoid colon
+2. Specimen type: 
+    A: Biopsy    B: biopsy    C: Biopsy   D: polypectomy   E: polypectomy
+3. Quantity: 
+    A: Two tissue fragments, up to 0.4x0.2x0.2 cm in size
+    B: Five tissue fragments, up to 0.3x0.2x0.2 cm in size
+    C: Two tissue fragments, up to 0.2x0.2x0.2 cm in size
+    D: Multiple tissue fragments, up to 1x0.7x0.7 cm in size
+    E: One tissue fragment, 0.4x0.3x0.3 cm in size
+4. Comment: Nil 
+All for section and labeled as:                  Jar 0
+    A1: ascending colon    B1: transverse colon
+    C1: descending colon   D1: sigmoid colon     E1: sigmoid colon
+MICROSCOPIC:
+1. Histological diagnosis:
+Neoplastic polyp
+I. Adenoma: 
+Tubular adenoma
+2. Histological grade:
+Low grade dysplasia (including mild and moderate dysplasia)
+3. Margins status (including stalk):
+Margin(s) cannot be assessed: sections B1 and D1
+Margin(s) uninvolved: sections A1, C1 and E1
+4. Comment: Nil</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+A: Tubular adenoma, Ascending colon, S/p biopsy and removal, 0.2-0.3cm.
+B: Tubular adenoma, Transverse colon, S/p biopsy and removal, 0.2-0.4cm.
+C: Tubular adenoma, Descending colon, S/p biopsy and removal, 0.2-0.3cm.
+D: Tubular adenoma, Sigmoid colon, S/p cold snaring polypectomy with hemoclipping, 1.0cm.
+E: Tubular adenoma, Sigmoid colon, S/p cold snaring polypectomy, 0.5cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 5 (less than 10mm: 4, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
+  <si>
+    <t>3 Years / 3y: 27 筆 (17 + 10)
+3-5 Years: 5 筆
+7-10 Years / 7-10y: 4 筆 (1 + 3)
+10 Years: 2 筆
+1 Year: 1 筆
+5-10 Years: 1 筆</t>
+  </si>
+  <si>
+    <t>P250690007692</t>
+  </si>
+  <si>
+    <t>Clinical Diagnosis                                      
+  Health examination
+ Indication                                              
+  國民健康署糞便潛血檢查陽性
+ Colon preparation agent                                 
+  Phosphosoda 類
+ Cleansing time:                                         
+  Split dose                                             
+ Cleansing Level:                                        
+  Good                                                   
+ Instrument:                                             
+  CF-HQ290I                  .3                
+ Insertion level:                                        
+  Cecum                                                  
+ Pre-mediction:                                          
+  Hyoscine butylbromide                                  
+ Sedation                                                
+  None
+ Accessibility:                                          
+  Easy                                                   
+ Anti-platelet/Anti-coagulant agents                     
+  Asprin(Tapal/Bokey)   Hold 9 days
+ Colonoscopic Findings                                   
+  The scope was inserted into cecum. There was a 0.5cm 0-Is 
+  adenoma, located at distal T-colon, cold snare polypectomy was 
+  done(A). There was a 1.0cm 0-Is lateral spreading tumor, 
+  located at sigmoid colon, mixed cold and hot snare polypectomy 
+  ws done(B). A 0.3cm 0-Is adenoma close by also removed by cold 
+  snare excision. Mixed hemorrhoids were also noted.
+ Diagnosis                                                                       檢體總數:                     2           
+  Tubular adenoma,O-ls,Transverse colon,0.5cm,(A),S/p cold snare 
+  polypectomy
+  Tubular adenoma,LST-NG(Laterally spreading tumor,non-granular 
+  type),Sigmoid colon,1.0cm,(B),S/p hot snare polypectomy,S/p 
+  cold snare polypectomy
+  Tubular adenoma,O-ls,Sigmoid colon,0.3cm,(B),S/p cold snare 
+  polypectomy
+ Complication                                            
+  Nil
+ Suggestion                                              
+  post polypectomy care;
+  regular CFS f/u</t>
+  </si>
+  <si>
+    <t>DIAGNOSIS
+Large intestine, T-colon (A), snare polypectomy
+   ----Tubular adenoma
+Large intestine, S-colon (B), snare polypectomy
+   ----Tubular adenoma
+GROSS DESCRIPTION
+   The specimen submitted consists of 2 bottles.
+   Bottle A contains a tissue fragment measuring 0.4 x 0.2 x 0.1 cm.
+   Bottle B contains 3 tissue fragments measuring up to 0.9 x 0.5 x 0.5 cm.
+   All for section.
+MICROSCOPIC DESCRIPTION
+   Sections of specimens A and B both show polypoid colonic mucosa/e with adenomatous glands.</t>
+  </si>
+  <si>
+    <t>1. Original Report:
+------------------------------------------------------------
+Here are the integrated labels:
+A: Tubular adenoma, T-colon, S/p cold snare polypectomy, 0.5cm.
+B: Tubular adenoma, S-colon, S/p hot snare polypectomy and S/p cold snare polypectomy, 1.0cm.
+------------------------------------------------------------
+2. Clinical Findings Summary:
+------------------------------------------------------------
+Total Adenomas: 2 (less than 10mm: 1, 10-19mm: 1, greater than or equal to 20mm: 0)
+Total SSPs: 0 (less than 10mm: 0, greater than or equal to 10mm: 0)
+High-Risk Features:
+  - High-Grade Dysplasia (HGD): No
+  - Villous Features: No
+  - Piecemeal Resection: No
+------------------------------------------------------------
+3. 2020 USMSTF recommendation interval
+3 Years</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -4248,22 +4286,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -4289,68 +4315,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0000FF"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFDBDBDB"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -4403,10 +4384,10 @@
         <color rgb="FFA5A5A5"/>
       </left>
       <right style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFA5A5A5"/>
       </top>
       <bottom style="thin">
         <color rgb="FFA5A5A5"/>
@@ -4414,30 +4395,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFFF0000"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color rgb="FF00FF00"/>
+        <color rgb="FFA5A5A5"/>
       </right>
       <top style="thin">
-        <color rgb="FFFF0000"/>
+        <color rgb="FFA5A5A5"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFF0000"/>
+        <color rgb="FFA5A5A5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4447,7 +4413,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4466,18 +4432,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4487,42 +4441,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5654,7 +5607,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
@@ -5667,61 +5620,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>117</v>
+      <c r="A1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>1</v>
+        <v>170</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>SUBSTITUTE(E2, " Years", "y")</f>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="str">
         <f t="shared" ref="F3:F4" si="0">SUBSTITUTE(E3, " Years", "y")</f>
@@ -5729,62 +5682,62 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>120</v>
+      <c r="A4" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>7-10y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="A5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>121</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>SUBSTITUTE(E5, " Years", "y")</f>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="str">
         <f t="shared" ref="F6:F41" si="1">SUBSTITUTE(E6, " Years", "y")</f>
@@ -5792,20 +5745,20 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A7" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>120</v>
+      <c r="A7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="F7" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5813,20 +5766,20 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A8" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>9</v>
+      <c r="A8" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5834,20 +5787,20 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A9" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>130</v>
+      <c r="A9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F9" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5855,20 +5808,20 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>4</v>
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5876,20 +5829,20 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>9</v>
+      <c r="A11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5897,41 +5850,41 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>121</v>
+      <c r="A12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F12" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A13" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>130</v>
+      <c r="A13" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="F13" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5939,41 +5892,41 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>10</v>
+      <c r="A14" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>7-10y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>9</v>
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F15" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5981,20 +5934,20 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A16" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>9</v>
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F16" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6002,62 +5955,62 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>4</v>
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="str">
         <f t="shared" si="1"/>
         <v>3-5y</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="238" x14ac:dyDescent="0.15">
-      <c r="A18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>10</v>
+    <row r="18" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>7-10y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>4</v>
+      <c r="A19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6065,62 +6018,62 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>121</v>
+      <c r="A20" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="F20" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>120</v>
+      <c r="A21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F21" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>7-10y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>120</v>
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="F22" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6128,20 +6081,20 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>9</v>
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6149,103 +6102,103 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A24" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>121</v>
+      <c r="A24" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F24" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A25" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>119</v>
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A26" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>4</v>
+      <c r="A26" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F26" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A27" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>10</v>
+      <c r="A27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="F27" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>7-10y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A28" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>130</v>
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="F28" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6253,20 +6206,20 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A29" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>130</v>
+      <c r="A29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F29" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6274,20 +6227,20 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A30" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>9</v>
+      <c r="A30" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F30" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6295,41 +6248,41 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A31" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>121</v>
+      <c r="A31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="F31" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>3-5y</v>
+        <v>7-10y</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A32" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>4</v>
+      <c r="A32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="F32" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6337,20 +6290,20 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A33" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>93</v>
+      <c r="A33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="F33" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6358,20 +6311,20 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A34" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>9</v>
+      <c r="A34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F34" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6379,41 +6332,41 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A35" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>10</v>
+      <c r="A35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>7-10y</v>
+        <v>10y</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="D36" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>130</v>
+      <c r="E36" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F36" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6421,20 +6374,20 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A37" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>130</v>
+      <c r="A37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F37" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6442,20 +6395,20 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A38" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>31</v>
+      <c r="A38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="F38" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6463,41 +6416,41 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A39" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>121</v>
+      <c r="A39" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>3-5y</v>
+        <v>3y</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A40" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>9</v>
+      <c r="A40" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F40" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6505,24 +6458,29 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="409.6" x14ac:dyDescent="0.15">
-      <c r="A41" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>120</v>
+      <c r="A41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="F41" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>7-10y</v>
+        <v>3y</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="175" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="20" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
